--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8642,13 +8642,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BF6C81E-0D71-4705-B02D-03D2D301B281}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A69048A-FE9A-4547-B799-0913FED60783}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B429926D-8763-49D6-AE3A-D7D9A3EFECAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F706AEFA-B1CD-430D-84D8-22CA09D4DBE5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D071264C-CB3B-418A-BE16-40A8650BF8CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813CB447-FC46-4A66-96F2-63C6F9CBC36C}"/>
 </file>
--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5429966-CDA3-4EB8-983D-14BA55C2DA54}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7D28D1-374A-491A-94D5-03DC69F67134}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="113">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>09:00/17:30</t>
+  </si>
+  <si>
+    <t>07:55/14:00</t>
   </si>
 </sst>
 </file>
@@ -773,7 +776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -808,31 +811,7 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -842,16 +821,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -860,38 +833,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -964,6 +912,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6562,110 +6564,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="22" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="23"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25" t="s">
+      <c r="A7" s="56"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="54" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -6682,10 +6684,10 @@
       <c r="G8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -6700,10 +6702,10 @@
       <c r="G9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -6716,10 +6718,10 @@
         <v>15</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="28"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -6728,14 +6730,14 @@
       <c r="E11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="20" t="s">
         <v>111</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="28"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
@@ -6744,278 +6746,278 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="28"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25" t="s">
+      <c r="A13" s="56"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="23"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25" t="s">
+      <c r="A15" s="56"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21" t="s">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="23"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25" t="s">
+      <c r="A17" s="56"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="26"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="23"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25" t="s">
+      <c r="A19" s="56"/>
+      <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="23" t="s">
+      <c r="G20" s="13"/>
+      <c r="H20" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="37" t="s">
+      <c r="A21" s="56"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26" t="s">
+      <c r="G21" s="16"/>
+      <c r="H21" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="54" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="42" t="s">
+      <c r="D22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="63" t="s">
+      <c r="E22" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="23" t="s">
         <v>38</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="28"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="63" t="s">
+      <c r="E23" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="23" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="1"/>
-      <c r="H23" s="28"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="B24" s="44" t="s">
+      <c r="A24" s="55"/>
+      <c r="B24" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="64" t="s">
+      <c r="E24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="42"/>
+      <c r="F24" s="23"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="28"/>
+      <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="B25" s="42" t="s">
+      <c r="A25" s="55"/>
+      <c r="B25" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="63" t="s">
+      <c r="E25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="42"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="28"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="42"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="28"/>
+      <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25" t="s">
+      <c r="A27" s="56"/>
+      <c r="B27" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="26"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="45" t="s">
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="45" t="s">
+      <c r="G28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="46" t="s">
+      <c r="H28" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="47" t="s">
+      <c r="A29" s="56"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="48" t="s">
+      <c r="G29" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="H29" s="49" t="s">
+      <c r="H29" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="54" t="s">
         <v>50</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -7028,18 +7030,18 @@
         <v>15</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="50" t="s">
+      <c r="G30" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="51" t="s">
+      <c r="H30" s="32" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
+      <c r="A31" s="55"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
@@ -7050,532 +7052,530 @@
         <v>53</v>
       </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="52" t="s">
+      <c r="F31" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" s="51" t="s">
+      <c r="G31" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="32" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
+      <c r="A32" s="55"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="37" t="s">
         <v>54</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="51"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="36"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="38" t="s">
         <v>55</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="51"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21" t="s">
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="22"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="23"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25" t="s">
+      <c r="A35" s="56"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="26"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="19"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="19"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="19"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="50" t="s">
+      <c r="D39" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="50" t="s">
+      <c r="E39" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="31"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="28"/>
+      <c r="H39" s="18"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="B40" s="50" t="s">
+      <c r="A40" s="55"/>
+      <c r="B40" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="50" t="s">
+      <c r="D40" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E40" s="50" t="s">
+      <c r="E40" s="31" t="s">
         <v>24</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="28"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="B41" s="53" t="s">
+      <c r="A41" s="55"/>
+      <c r="B41" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="53" t="s">
+      <c r="C41" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="53" t="s">
+      <c r="D41" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="E41" s="53" t="s">
+      <c r="E41" s="34" t="s">
         <v>62</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="28"/>
+      <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="B42" s="50" t="s">
+      <c r="A42" s="55"/>
+      <c r="B42" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="50" t="s">
+      <c r="D42" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E42" s="50" t="s">
+      <c r="E42" s="31" t="s">
         <v>63</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="28"/>
+      <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="B43" s="53" t="s">
+      <c r="A43" s="55"/>
+      <c r="B43" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="53" t="s">
+      <c r="C43" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="53" t="s">
+      <c r="D43" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="53" t="s">
+      <c r="E43" s="34" t="s">
         <v>20</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="28"/>
+      <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="B44" s="50" t="s">
+      <c r="A44" s="55"/>
+      <c r="B44" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="50" t="s">
+      <c r="C44" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="D44" s="50" t="s">
+      <c r="D44" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="50" t="s">
+      <c r="E44" s="31" t="s">
         <v>64</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="H44" s="28"/>
+      <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="53" t="s">
+      <c r="A45" s="55"/>
+      <c r="B45" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="53" t="s">
+      <c r="C45" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="53" t="s">
+      <c r="D45" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="53" t="s">
+      <c r="E45" s="34" t="s">
         <v>62</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-      <c r="H45" s="28"/>
+      <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="B46" s="50" t="s">
+      <c r="A46" s="55"/>
+      <c r="B46" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="50" t="s">
+      <c r="D46" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E46" s="50" t="s">
+      <c r="E46" s="31" t="s">
         <v>65</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="28"/>
+      <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
-      <c r="B47" s="53" t="s">
+      <c r="A47" s="55"/>
+      <c r="B47" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="53" t="s">
+      <c r="C47" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="53" t="s">
+      <c r="D47" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="53" t="s">
+      <c r="E47" s="34" t="s">
         <v>20</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="28"/>
+      <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="50" t="s">
+      <c r="A48" s="55"/>
+      <c r="B48" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="C48" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="D48" s="50" t="s">
+      <c r="D48" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="E48" s="50" t="s">
+      <c r="E48" s="31" t="s">
         <v>66</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="28"/>
+      <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="53" t="s">
+      <c r="A49" s="55"/>
+      <c r="B49" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="C49" s="53" t="s">
+      <c r="C49" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="53" t="s">
+      <c r="D49" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="50"/>
+      <c r="E49" s="31"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="28"/>
+      <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="50" t="s">
+      <c r="A50" s="55"/>
+      <c r="B50" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="50" t="s">
+      <c r="C50" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D50" s="50" t="s">
+      <c r="D50" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E50" s="50"/>
+      <c r="E50" s="31"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="28"/>
+      <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="53" t="s">
+      <c r="A51" s="55"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="50"/>
+      <c r="E51" s="31"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="28"/>
+      <c r="H51" s="18"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24"/>
-      <c r="B52" s="48"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48" t="s">
+      <c r="A52" s="56"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="E52" s="48"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="26"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="23"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="24"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="26"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
+      <c r="A55" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="54" t="s">
+      <c r="B55" s="13"/>
+      <c r="C55" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="54" t="s">
+      <c r="D55" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="21"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="23"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="24"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="55" t="s">
+      <c r="A56" s="56"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D56" s="55" t="s">
+      <c r="D56" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="26"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="54" t="s">
         <v>73</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="58" t="s">
+      <c r="G57" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="H57" s="28" t="s">
+      <c r="H57" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="27"/>
+      <c r="A58" s="55"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="58" t="s">
+      <c r="G58" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="H58" s="28" t="s">
+      <c r="H58" s="18" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="27"/>
+      <c r="A59" s="55"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="61" t="s">
+      <c r="G59" s="39"/>
+      <c r="H59" s="42" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="27"/>
+      <c r="A60" s="55"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="59" t="s">
+      <c r="G60" s="39"/>
+      <c r="H60" s="40" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="27"/>
+      <c r="A61" s="55"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="29" t="s">
+      <c r="G61" s="39"/>
+      <c r="H61" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="27"/>
+      <c r="A62" s="55"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="28" t="s">
+      <c r="G62" s="39"/>
+      <c r="H62" s="18" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="27"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="61" t="s">
+      <c r="G63" s="39"/>
+      <c r="H63" s="42" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="24"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="60"/>
-      <c r="H64" s="62" t="s">
+      <c r="A64" s="56"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="43" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B65" s="32"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="33"/>
-      <c r="G65" s="33"/>
-      <c r="H65" s="34"/>
+      <c r="B65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="49"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="D66" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E66" s="21"/>
-      <c r="F66" s="45" t="s">
+      <c r="E66" s="13"/>
+      <c r="F66" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G66" s="45" t="s">
+      <c r="G66" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H66" s="46" t="s">
+      <c r="H66" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="27"/>
+      <c r="A67" s="55"/>
       <c r="B67" s="1" t="s">
         <v>82</v>
       </c>
@@ -7586,70 +7586,70 @@
         <v>51</v>
       </c>
       <c r="E67" s="1"/>
-      <c r="F67" s="52" t="s">
+      <c r="F67" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="G67" s="50" t="s">
+      <c r="G67" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="H67" s="51" t="s">
+      <c r="H67" s="32" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="27"/>
-      <c r="B68" s="56" t="s">
+      <c r="A68" s="55"/>
+      <c r="B68" s="37" t="s">
         <v>54</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="50"/>
-      <c r="G68" s="50"/>
-      <c r="H68" s="51"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="32"/>
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="24"/>
-      <c r="B69" s="55" t="s">
+      <c r="A69" s="56"/>
+      <c r="B69" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="49"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="30"/>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="19"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="52"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C71" s="21" t="s">
+      <c r="C71" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="23"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="15"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="27"/>
+      <c r="A72" s="55"/>
       <c r="B72" s="1" t="s">
         <v>85</v>
       </c>
@@ -7660,10 +7660,10 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="28"/>
+      <c r="H72" s="18"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="27"/>
+      <c r="A73" s="55"/>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
@@ -7674,59 +7674,58 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="28"/>
+      <c r="H73" s="18"/>
     </row>
     <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="24"/>
-      <c r="B74" s="25" t="s">
+      <c r="A74" s="56"/>
+      <c r="B74" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C74" s="25" t="s">
+      <c r="C74" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="26"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="17"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="30" t="s">
+      <c r="A75" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B75" s="57" t="s">
+      <c r="B75" s="38" t="s">
         <v>54</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="58" t="s">
+      <c r="G75" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="H75" s="59" t="s">
+      <c r="H75" s="40" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="27"/>
-      <c r="B76" s="57" t="s">
+      <c r="A76" s="55"/>
+      <c r="B76" s="38" t="s">
         <v>55</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="58" t="s">
+      <c r="G76" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="H76" s="59" t="s">
+      <c r="H76" s="40" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="27"/>
-      <c r="B77" s="57"/>
+      <c r="A77" s="55"/>
+      <c r="B77" s="38"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -7734,128 +7733,123 @@
       <c r="G77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H77" s="29" t="s">
+      <c r="H77" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="24"/>
-      <c r="B78" s="55"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25" t="s">
+      <c r="A78" s="56"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H78" s="26" t="s">
+      <c r="H78" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18"/>
-      <c r="H79" s="19"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="52"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="18"/>
-      <c r="H80" s="19"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="51"/>
+      <c r="D80" s="51"/>
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+      <c r="G80" s="51"/>
+      <c r="H80" s="52"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="19"/>
+      <c r="B81" s="50"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="52"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="B82" s="21"/>
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21" t="s">
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F82" s="22"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="23" t="s">
+      <c r="F82" s="14"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="24"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="26" t="s">
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="18"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="18"/>
-      <c r="H84" s="19"/>
+      <c r="B84" s="50"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="52"/>
     </row>
     <row r="85" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
+      <c r="B85" s="53"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B85:H85"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="B80:H80"/>
-    <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B84:H84"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A57:A64"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
     <mergeCell ref="A39:A52"/>
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
@@ -7863,16 +7857,21 @@
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A57:A64"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B38:H38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7891,20 +7890,20 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -8477,6 +8476,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="83" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="584bf6b77295f7da4f9cf4ac656056b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0744868ac059cd1623b27209cff1bde4" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -8621,15 +8629,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8642,13 +8641,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A69048A-FE9A-4547-B799-0913FED60783}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F706AEFA-B1CD-430D-84D8-22CA09D4DBE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F706AEFA-B1CD-430D-84D8-22CA09D4DBE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A69048A-FE9A-4547-B799-0913FED60783}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813CB447-FC46-4A66-96F2-63C6F9CBC36C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813CB447-FC46-4A66-96F2-63C6F9CBC36C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7D28D1-374A-491A-94D5-03DC69F67134}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E56646FC-5B82-40EB-9557-4D20D77663FA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="113">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -168,9 +168,6 @@
     <t>07:55/17:00</t>
   </si>
   <si>
-    <t>08:15/14:00</t>
-  </si>
-  <si>
     <t>09:00/19:00</t>
   </si>
   <si>
@@ -361,6 +358,9 @@
   </si>
   <si>
     <t>07:55/14:00</t>
+  </si>
+  <si>
+    <t>15:00/18:00</t>
   </si>
 </sst>
 </file>
@@ -517,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -772,6 +772,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -855,9 +866,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -968,6 +976,9 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2493,13 +2504,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2537,13 +2548,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2581,101 +2592,57 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2713,13 +2680,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2757,13 +2724,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2801,13 +2768,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2833,50 +2800,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2900,54 +2823,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2988,10 +2867,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3009,1062 +2888,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4088,10 +2911,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4121,21 +2944,1121 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4153,94 +4076,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4264,10 +4099,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4285,6 +4120,94 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4308,10 +4231,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4339,428 +4262,252 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4781,21 +4528,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4823,76 +4570,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4913,21 +4704,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4955,164 +4746,76 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5133,21 +4836,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5177,6 +4880,50 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -5188,19 +4935,107 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5221,21 +5056,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5263,260 +5098,260 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5540,10 +5375,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5561,50 +5396,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5628,10 +5419,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5659,23 +5450,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5716,6 +5551,94 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -5749,13 +5672,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5793,13 +5716,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6176,6 +6099,710 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10069286" y="762000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C4E0D82-F8FE-49F6-BBB1-FCA34AE6B9DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14627679" y="5660571"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F62859C-F136-4142-9731-F5C10BBDE096}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14627679" y="5660571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CE02145-BF9F-4959-BECC-56E863A9381B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14627679" y="6041571"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7974EDE5-CEB5-456A-A2EE-6E0C148C713E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17553214" y="6041571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE7641C-186C-4AD1-9628-59490CFBAFE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20478750" y="6041571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3746426-C2AE-4C70-8D61-5EC2073BDDD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14627679" y="6041571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B47883-26F3-4071-8B26-A0E4FCE209F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17553214" y="6422571"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86860902-EEA3-4EF1-BC72-9D15FDB5CA7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17553214" y="6422571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="128" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD5157ED-8C59-4198-933D-F108F02B419C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14627679" y="6041571"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="129" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EC240F8-4C3B-44F5-AD04-FA9E2A88F91F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17553214" y="6041571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="130" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8039DC6-825D-422B-8B85-6572530FC6BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20478750" y="6041571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="131" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8DA95EA-A40E-4F86-ABFA-ABA2228F4786}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14627679" y="6041571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="132" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EA90DC-F1A4-4E9B-8A32-F437ADF667D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17553214" y="6422571"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="133" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C34D350-395B-40E2-B462-0B25CC5D1E09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17553214" y="6422571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="134" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C23EDF8-EE02-4C1C-A010-303C5F5C5A4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11702143" y="16178893"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="135" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{355868F0-8922-4754-BD84-F93D4DDB73DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5851071" y="13035643"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6557,35 +7184,35 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
@@ -6626,18 +7253,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="62"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="61"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="56" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -6653,7 +7280,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="56"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -6667,7 +7294,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -6687,7 +7314,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
+      <c r="A9" s="54"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -6705,7 +7332,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -6721,7 +7348,7 @@
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -6731,13 +7358,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
@@ -6749,7 +7376,7 @@
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="56"/>
+      <c r="A13" s="55"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
@@ -6761,7 +7388,7 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="56" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -6775,7 +7402,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
+      <c r="A15" s="55"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -6787,7 +7414,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="56" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -6801,7 +7428,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="56"/>
+      <c r="A17" s="55"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -6813,7 +7440,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="56" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -6833,7 +7460,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="56"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -6851,12 +7478,14 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="56" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
+      <c r="D20" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13" t="s">
         <v>15</v>
@@ -6867,10 +7496,12 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="56"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+      <c r="D21" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="E21" s="16"/>
       <c r="F21" s="21" t="s">
         <v>35</v>
@@ -6881,19 +7512,19 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="53" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="43" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="43" t="s">
         <v>37</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -6903,17 +7534,17 @@
       <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="55"/>
+      <c r="A23" s="54"/>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="44" t="s">
+      <c r="E23" s="43" t="s">
         <v>40</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -6923,17 +7554,17 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
+      <c r="A24" s="54"/>
       <c r="B24" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="45" t="s">
+      <c r="E24" s="44" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="23"/>
@@ -6941,17 +7572,17 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="55"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="43" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="23"/>
@@ -6959,884 +7590,912 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="55"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="56"/>
+      <c r="A27" s="55"/>
       <c r="B27" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="56" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="26" t="s">
+      <c r="G28" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="27" t="s">
+      <c r="H28" s="31" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="28" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="64"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="G29" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="H29" s="30" t="s">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="64"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="31"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="57"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="31"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="56" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="54" t="s">
+      <c r="B32" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="54"/>
+      <c r="B33" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
-      <c r="B31" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="55"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="58"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="38" t="s">
-        <v>55</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32"/>
+      <c r="F33" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13" t="s">
+      <c r="A34" s="54"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="31"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="55"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="H35" s="29"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="15"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="17"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="50"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="52"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="52"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="49"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="51"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="49"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="51"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="49"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="51"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="52"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="31" t="s">
+      <c r="B41" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C41" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D41" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="31" t="s">
+      <c r="E41" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="18"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="55"/>
-      <c r="B40" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="18"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="55"/>
-      <c r="B41" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="55"/>
-      <c r="B42" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>63</v>
+      <c r="A42" s="54"/>
+      <c r="B42" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="55"/>
-      <c r="B43" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="34" t="s">
-        <v>20</v>
+      <c r="A43" s="54"/>
+      <c r="B43" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="55"/>
-      <c r="B44" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" s="31" t="s">
-        <v>64</v>
+      <c r="A44" s="54"/>
+      <c r="B44" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="55"/>
-      <c r="B45" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E45" s="34" t="s">
-        <v>62</v>
+      <c r="A45" s="54"/>
+      <c r="B45" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>20</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="55"/>
-      <c r="B46" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E46" s="31" t="s">
-        <v>65</v>
+      <c r="A46" s="54"/>
+      <c r="B46" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>63</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="55"/>
-      <c r="B47" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D47" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="34" t="s">
-        <v>20</v>
+      <c r="A47" s="54"/>
+      <c r="B47" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="55"/>
-      <c r="B48" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="31" t="s">
-        <v>66</v>
+      <c r="A48" s="54"/>
+      <c r="B48" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>64</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="55"/>
-      <c r="B49" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="31"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>20</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="55"/>
-      <c r="B50" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E50" s="31"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>65</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="55"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="31"/>
+      <c r="A51" s="54"/>
+      <c r="B51" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="30"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="18"/>
     </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="56"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="17"/>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="54"/>
+      <c r="B52" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="30"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="18"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="15"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="30"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="18"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="56"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
+      <c r="A54" s="55"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="28"/>
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
       <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="57" t="s">
-        <v>70</v>
+      <c r="A55" s="56" t="s">
+        <v>68</v>
       </c>
       <c r="B55" s="13"/>
-      <c r="C55" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="D55" s="35" t="s">
-        <v>54</v>
-      </c>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
       <c r="E55" s="13"/>
       <c r="F55" s="14"/>
       <c r="G55" s="13"/>
       <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="56"/>
+      <c r="A56" s="55"/>
       <c r="B56" s="16"/>
-      <c r="C56" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D56" s="36" t="s">
-        <v>72</v>
-      </c>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
       <c r="G56" s="16"/>
       <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="G57" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="H57" s="18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="15"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="55"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="H58" s="18" t="s">
-        <v>76</v>
-      </c>
+      <c r="B58" s="16"/>
+      <c r="C58" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="17"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="55"/>
+      <c r="A59" s="53" t="s">
+        <v>72</v>
+      </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="42" t="s">
-        <v>74</v>
+      <c r="G59" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="55"/>
+      <c r="A60" s="54"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="40" t="s">
-        <v>77</v>
+      <c r="G60" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="55"/>
+      <c r="A61" s="54"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="19" t="s">
-        <v>15</v>
+      <c r="G61" s="38"/>
+      <c r="H61" s="41" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="55"/>
+      <c r="A62" s="54"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="18" t="s">
-        <v>78</v>
+      <c r="G62" s="38"/>
+      <c r="H62" s="39" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="55"/>
+      <c r="A63" s="54"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="42" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="56"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="43" t="s">
+      <c r="G63" s="38"/>
+      <c r="H63" s="19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="54"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="54"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="55"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="12" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12" t="s">
+      <c r="B67" s="46"/>
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="48"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B65" s="47"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="49"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="57" t="s">
+      <c r="B68" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="54"/>
+      <c r="B69" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="C69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="G69" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="H69" s="31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="54"/>
+      <c r="B70" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" s="31"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="55"/>
+      <c r="B71" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="28"/>
+      <c r="G71" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="H71" s="29"/>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="49"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
+      <c r="G72" s="50"/>
+      <c r="H72" s="51"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="15"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="54"/>
+      <c r="B74" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="18"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="54"/>
+      <c r="B75" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C75" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H66" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="55"/>
-      <c r="B67" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E67" s="1"/>
-      <c r="F67" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="G67" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H67" s="32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="55"/>
-      <c r="B68" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="32"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="56"/>
-      <c r="B69" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="30"/>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B70" s="50"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="52"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="15"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="55"/>
-      <c r="B72" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="18"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="55"/>
-      <c r="B73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="18"/>
-    </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="56"/>
-      <c r="B74" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
-      <c r="H74" s="17"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="B75" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="G75" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="H75" s="40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="18"/>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="55"/>
-      <c r="B76" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="H76" s="40" t="s">
-        <v>88</v>
-      </c>
+      <c r="B76" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="17"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="55"/>
-      <c r="B77" s="38"/>
+      <c r="A77" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" s="37" t="s">
+        <v>53</v>
+      </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H77" s="39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="54"/>
+      <c r="B78" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="H78" s="39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="54"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H77" s="19" t="s">
+      <c r="H79" s="19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="56"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16" t="s">
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="55"/>
+      <c r="B80" s="35"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H80" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H78" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B79" s="50"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="52"/>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B80" s="50"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="51"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="51"/>
-      <c r="G80" s="51"/>
-      <c r="H80" s="52"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="49"/>
+      <c r="C81" s="50"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="51"/>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="49"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="51"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" s="49"/>
+      <c r="C83" s="50"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="51"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="50"/>
-      <c r="C81" s="51"/>
-      <c r="D81" s="51"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="51"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="52"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="57" t="s">
+      <c r="B84" s="13"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="14"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="55"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E85" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F85" s="16"/>
+      <c r="G85" s="16"/>
+      <c r="H85" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="14"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="56"/>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="17" t="s">
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="12" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" s="50"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="51"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="52"/>
-    </row>
-    <row r="85" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="53"/>
-      <c r="C85" s="53"/>
-      <c r="D85" s="53"/>
-      <c r="E85" s="53"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="53"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="50"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
+      <c r="H86" s="51"/>
+    </row>
+    <row r="87" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -7850,28 +8509,28 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A39:A52"/>
-    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A41:A54"/>
     <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A57:A64"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="B85:H85"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A77:A80"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A59:A66"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="B87:H87"/>
     <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B84:H84"/>
-    <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B82:H82"/>
+    <mergeCell ref="B83:H83"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B72:H72"/>
     <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7890,36 +8549,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="64" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8077,7 +8736,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8094,7 +8753,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8111,7 +8770,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8128,7 +8787,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8145,7 +8804,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8162,7 +8821,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8179,7 +8838,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8196,7 +8855,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8213,7 +8872,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8230,7 +8889,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8247,7 +8906,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8264,7 +8923,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8281,7 +8940,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8298,7 +8957,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8315,7 +8974,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8332,7 +8991,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8349,7 +9008,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8366,7 +9025,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8383,7 +9042,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -8433,40 +9092,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E56646FC-5B82-40EB-9557-4D20D77663FA}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7D28D1-374A-491A-94D5-03DC69F67134}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="113">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -168,6 +168,9 @@
     <t>07:55/17:00</t>
   </si>
   <si>
+    <t>08:15/14:00</t>
+  </si>
+  <si>
     <t>09:00/19:00</t>
   </si>
   <si>
@@ -358,9 +361,6 @@
   </si>
   <si>
     <t>07:55/14:00</t>
-  </si>
-  <si>
-    <t>15:00/18:00</t>
   </si>
 </sst>
 </file>
@@ -517,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -772,17 +772,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -866,6 +855,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -976,9 +968,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2504,21 +2493,153 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2546,103 +2667,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2680,13 +2713,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2724,13 +2757,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2768,13 +2801,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2800,6 +2833,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2823,10 +2900,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2867,10 +2988,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2888,6 +3009,1062 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2911,10 +4088,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2944,21 +4121,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2986,516 +4163,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3516,566 +4209,38 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4099,10 +4264,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4120,94 +4285,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4231,10 +4308,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4262,23 +4339,243 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4306,67 +4603,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4394,67 +4647,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4482,32 +4735,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4528,21 +4781,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4570,155 +4823,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4746,76 +4955,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4836,21 +5133,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4880,197 +5177,65 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5098,32 +5263,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5144,21 +5441,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5186,172 +5483,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5375,10 +5540,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5396,6 +5561,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5419,10 +5628,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5450,67 +5659,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5551,10 +5716,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5582,84 +5747,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15103929" y="12314464"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5672,57 +5793,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15103929" y="12314464"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6099,710 +6176,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10069286" y="762000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C4E0D82-F8FE-49F6-BBB1-FCA34AE6B9DD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F62859C-F136-4142-9731-F5C10BBDE096}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CE02145-BF9F-4959-BECC-56E863A9381B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7974EDE5-CEB5-456A-A2EE-6E0C148C713E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE7641C-186C-4AD1-9628-59490CFBAFE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3746426-C2AE-4C70-8D61-5EC2073BDDD0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B47883-26F3-4071-8B26-A0E4FCE209F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86860902-EEA3-4EF1-BC72-9D15FDB5CA7C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD5157ED-8C59-4198-933D-F108F02B419C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EC240F8-4C3B-44F5-AD04-FA9E2A88F91F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="130" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8039DC6-825D-422B-8B85-6572530FC6BF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="131" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8DA95EA-A40E-4F86-ABFA-ABA2228F4786}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="132" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EA90DC-F1A4-4E9B-8A32-F437ADF667D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="133" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C34D350-395B-40E2-B462-0B25CC5D1E09}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="134" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C23EDF8-EE02-4C1C-A010-303C5F5C5A4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11702143" y="16178893"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="135" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{355868F0-8922-4754-BD84-F93D4DDB73DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5851071" y="13035643"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7184,35 +6557,35 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
@@ -7253,18 +6626,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7280,7 +6653,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7294,7 +6667,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="54" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7314,7 +6687,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7332,7 +6705,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7348,7 +6721,7 @@
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7358,13 +6731,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
@@ -7376,7 +6749,7 @@
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
@@ -7388,7 +6761,7 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7402,7 +6775,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
+      <c r="A15" s="56"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7414,7 +6787,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="57" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7428,7 +6801,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
+      <c r="A17" s="56"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7440,7 +6813,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="57" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7460,7 +6833,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7478,14 +6851,12 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13" t="s">
         <v>15</v>
@@ -7496,12 +6867,10 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55"/>
+      <c r="A21" s="56"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
-      <c r="D21" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="21" t="s">
         <v>35</v>
@@ -7512,19 +6881,19 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="54" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="44" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="44" t="s">
         <v>37</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -7534,17 +6903,17 @@
       <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -7554,17 +6923,17 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="45" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="23"/>
@@ -7572,17 +6941,17 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="44" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="23"/>
@@ -7590,912 +6959,884 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="57" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="32" t="s">
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="56"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H29" s="31" t="s">
+      <c r="G29" s="29" t="s">
         <v>48</v>
       </c>
+      <c r="H29" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="64"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="33" t="s">
+      <c r="F30" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="31"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="G30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="55"/>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30" t="s">
+      <c r="F31" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="H31" s="31"/>
+      <c r="H31" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="54"/>
-      <c r="B33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>51</v>
+      <c r="A32" s="55"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="58"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="38" t="s">
+        <v>55</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H33" s="31" t="s">
-        <v>48</v>
-      </c>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="54"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="31"/>
+      <c r="A34" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="35" t="s">
-        <v>54</v>
-      </c>
+      <c r="C35" s="16"/>
       <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H35" s="29"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="15"/>
+      <c r="E35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17"/>
+      <c r="A37" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="51"/>
+        <v>59</v>
+      </c>
+      <c r="B38" s="50"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="55"/>
+      <c r="B40" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>20</v>
-      </c>
+      <c r="A41" s="55"/>
+      <c r="B41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="54"/>
-      <c r="B42" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>24</v>
+      <c r="A42" s="55"/>
+      <c r="B42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
-      <c r="B43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>61</v>
+      <c r="A43" s="55"/>
+      <c r="B43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>62</v>
+      <c r="A44" s="55"/>
+      <c r="B44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>64</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="54"/>
-      <c r="B45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="33" t="s">
-        <v>20</v>
+      <c r="A45" s="55"/>
+      <c r="B45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>62</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>63</v>
+      <c r="A46" s="55"/>
+      <c r="B46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="33" t="s">
-        <v>61</v>
+      <c r="A47" s="55"/>
+      <c r="B47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>64</v>
+      <c r="A48" s="55"/>
+      <c r="B48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>20</v>
-      </c>
+      <c r="A49" s="55"/>
+      <c r="B49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="31"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
-      <c r="B50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>65</v>
-      </c>
+      <c r="A50" s="55"/>
+      <c r="B50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="31"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="54"/>
-      <c r="B51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="30"/>
+      <c r="A51" s="55"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="31"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="18"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="54"/>
-      <c r="B52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="18"/>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="56"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="29"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="54"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="18"/>
+      <c r="A53" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="28"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
       <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="56" t="s">
-        <v>68</v>
+      <c r="A55" s="57" t="s">
+        <v>70</v>
       </c>
       <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
+      <c r="C55" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>54</v>
+      </c>
       <c r="E55" s="13"/>
       <c r="F55" s="14"/>
       <c r="G55" s="13"/>
       <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="55"/>
+      <c r="A56" s="56"/>
       <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
+      <c r="C56" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>72</v>
+      </c>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
       <c r="G56" s="16"/>
       <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="G57" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="55"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="17"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
-        <v>72</v>
-      </c>
+      <c r="A59" s="55"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="G59" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>15</v>
+      <c r="F59" s="1"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="42" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
+      <c r="A60" s="55"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>75</v>
+      <c r="G60" s="39"/>
+      <c r="H60" s="40" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="54"/>
+      <c r="A61" s="55"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="41" t="s">
-        <v>73</v>
+      <c r="G61" s="39"/>
+      <c r="H61" s="19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54"/>
+      <c r="A62" s="55"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="39" t="s">
-        <v>76</v>
+      <c r="G62" s="39"/>
+      <c r="H62" s="18" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="19" t="s">
+      <c r="G63" s="39"/>
+      <c r="H63" s="42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="56"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="49"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="42" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" s="46"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="48"/>
+      <c r="C66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="55"/>
+      <c r="B67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H67" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="13" t="s">
+      <c r="A68" s="55"/>
+      <c r="B68" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="56"/>
+      <c r="B69" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="30"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" s="50"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="52"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="15"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="55"/>
+      <c r="B72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="18"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="55"/>
+      <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
-      <c r="B69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G69" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H69" s="31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="54"/>
-      <c r="B70" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
-      <c r="B71" s="35" t="s">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="56"/>
+      <c r="B74" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="17"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H71" s="29"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="49"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="51"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="15"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="54"/>
-      <c r="B74" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="18"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="54"/>
-      <c r="B75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
-    </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G75" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="55"/>
-      <c r="B76" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="17"/>
+      <c r="B76" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="40" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>53</v>
-      </c>
+      <c r="A77" s="55"/>
+      <c r="B77" s="38"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="G77" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="54"/>
-      <c r="B78" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="54"/>
-      <c r="B79" s="37"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="2" t="s">
+      <c r="F77" s="1"/>
+      <c r="G77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="H77" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="56"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="52"/>
+    </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="55"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>89</v>
-      </c>
+      <c r="A80" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="50"/>
+      <c r="C80" s="51"/>
+      <c r="D80" s="51"/>
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+      <c r="G80" s="51"/>
+      <c r="H80" s="52"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="49"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="51"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B82" s="49"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="51"/>
+        <v>93</v>
+      </c>
+      <c r="B81" s="50"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="52"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="14"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B83" s="49"/>
-      <c r="C83" s="50"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="51"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="55"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="49"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="51"/>
-    </row>
-    <row r="87" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" s="50"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="52"/>
+    </row>
+    <row r="85" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="53"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -8509,28 +7850,28 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="A39:A52"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A59:A66"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A57:A64"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
     <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8549,36 +7890,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+      <c r="B4" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="B5" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8736,7 +8077,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8753,7 +8094,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8770,7 +8111,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8787,7 +8128,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8804,7 +8145,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8821,7 +8162,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8838,7 +8179,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8855,7 +8196,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8872,7 +8213,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8889,7 +8230,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8906,7 +8247,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8923,7 +8264,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8940,7 +8281,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8957,7 +8298,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8974,7 +8315,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8991,7 +8332,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9008,7 +8349,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9025,7 +8366,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9042,7 +8383,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9092,40 +8433,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E56646FC-5B82-40EB-9557-4D20D77663FA}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36791057-EDBA-47EC-95E7-7280EFA45539}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="115">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -354,13 +354,19 @@
     <t>14/04/2026 16:04</t>
   </si>
   <si>
-    <t>09:00/17:30</t>
-  </si>
-  <si>
     <t>07:55/14:00</t>
   </si>
   <si>
     <t>15:00/18:00</t>
+  </si>
+  <si>
+    <t>INVEN</t>
+  </si>
+  <si>
+    <t>06:00/07:30</t>
+  </si>
+  <si>
+    <t>09:00/16:00</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,6 +519,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -787,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -979,6 +991,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1358,50 +1379,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
@@ -5980,94 +5957,6 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0D3522B-1460-4B06-A15B-6831EAAAB1B0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15103929" y="1143000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDF2039-6A37-48FF-AE60-3E6609376C72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7551964" y="1143000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6803,6 +6692,138 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5851071" y="13035643"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="136" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{032F124A-F13E-4A50-A618-95C926A42538}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="2867025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="137" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD0ED26-4249-4AD5-AC50-52F58791D4D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="3248025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="138" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8078E310-A965-4F05-BB5A-6E442BA5630B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="3629025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7305,8 +7326,8 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
+      <c r="F8" s="66" t="s">
+        <v>112</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7323,8 +7344,8 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>21</v>
+      <c r="F9" s="67" t="s">
+        <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7341,8 +7362,8 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>15</v>
+      <c r="F10" s="65" t="s">
+        <v>19</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
@@ -7358,7 +7379,7 @@
         <v>25</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="18"/>
@@ -7371,7 +7392,9 @@
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="F12" s="65" t="s">
+        <v>15</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
@@ -7383,7 +7406,9 @@
         <v>26</v>
       </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="F13" s="20" t="s">
+        <v>114</v>
+      </c>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
     </row>
@@ -7641,7 +7666,7 @@
         <v>47</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H29" s="31" t="s">
         <v>48</v>
@@ -7667,7 +7692,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="30"/>
       <c r="G31" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H31" s="31"/>
     </row>
@@ -7707,7 +7732,7 @@
         <v>47</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H33" s="31" t="s">
         <v>48</v>
@@ -7737,7 +7762,7 @@
       <c r="E35" s="16"/>
       <c r="F35" s="28"/>
       <c r="G35" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H35" s="29"/>
     </row>
@@ -8241,7 +8266,7 @@
         <v>47</v>
       </c>
       <c r="G69" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H69" s="31" t="s">
         <v>48</v>
@@ -8271,7 +8296,7 @@
       <c r="E71" s="16"/>
       <c r="F71" s="28"/>
       <c r="G71" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H71" s="29"/>
     </row>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36791057-EDBA-47EC-95E7-7280EFA45539}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7D28D1-374A-491A-94D5-03DC69F67134}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="113">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -168,6 +168,9 @@
     <t>07:55/17:00</t>
   </si>
   <si>
+    <t>08:15/14:00</t>
+  </si>
+  <si>
     <t>09:00/19:00</t>
   </si>
   <si>
@@ -354,19 +357,10 @@
     <t>14/04/2026 16:04</t>
   </si>
   <si>
+    <t>09:00/17:30</t>
+  </si>
+  <si>
     <t>07:55/14:00</t>
-  </si>
-  <si>
-    <t>15:00/18:00</t>
-  </si>
-  <si>
-    <t>INVEN</t>
-  </si>
-  <si>
-    <t>06:00/07:30</t>
-  </si>
-  <si>
-    <t>09:00/16:00</t>
   </si>
 </sst>
 </file>
@@ -480,7 +474,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,14 +516,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -784,22 +772,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -878,6 +855,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -988,18 +968,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1379,6 +1347,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
@@ -2481,21 +2493,153 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2523,103 +2667,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2657,13 +2713,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2701,13 +2757,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2745,13 +2801,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2777,6 +2833,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2800,10 +2900,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2844,10 +2988,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2865,6 +3009,1062 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2888,10 +4088,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2921,21 +4121,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2963,516 +4163,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3493,566 +4209,38 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4076,10 +4264,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4097,94 +4285,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4208,10 +4308,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4239,23 +4339,243 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4283,67 +4603,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4371,67 +4647,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4459,32 +4735,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4505,21 +4781,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4547,155 +4823,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4723,76 +4955,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4813,21 +5133,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4857,197 +5177,65 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5075,32 +5263,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5121,21 +5441,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5163,172 +5483,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5352,10 +5540,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5373,6 +5561,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5396,10 +5628,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5427,67 +5659,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5528,10 +5716,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5559,84 +5747,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15103929" y="12314464"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5649,57 +5793,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15103929" y="12314464"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5957,6 +6057,94 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0D3522B-1460-4B06-A15B-6831EAAAB1B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15103929" y="1143000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDF2039-6A37-48FF-AE60-3E6609376C72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7551964" y="1143000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -5988,842 +6176,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10069286" y="762000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C4E0D82-F8FE-49F6-BBB1-FCA34AE6B9DD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F62859C-F136-4142-9731-F5C10BBDE096}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CE02145-BF9F-4959-BECC-56E863A9381B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7974EDE5-CEB5-456A-A2EE-6E0C148C713E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE7641C-186C-4AD1-9628-59490CFBAFE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3746426-C2AE-4C70-8D61-5EC2073BDDD0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B47883-26F3-4071-8B26-A0E4FCE209F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86860902-EEA3-4EF1-BC72-9D15FDB5CA7C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD5157ED-8C59-4198-933D-F108F02B419C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EC240F8-4C3B-44F5-AD04-FA9E2A88F91F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="130" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8039DC6-825D-422B-8B85-6572530FC6BF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="131" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8DA95EA-A40E-4F86-ABFA-ABA2228F4786}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="132" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EA90DC-F1A4-4E9B-8A32-F437ADF667D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="133" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C34D350-395B-40E2-B462-0B25CC5D1E09}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="134" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C23EDF8-EE02-4C1C-A010-303C5F5C5A4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11702143" y="16178893"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="135" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{355868F0-8922-4754-BD84-F93D4DDB73DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5851071" y="13035643"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="136" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{032F124A-F13E-4A50-A618-95C926A42538}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="2867025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="137" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD0ED26-4249-4AD5-AC50-52F58791D4D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="3248025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="138" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8078E310-A965-4F05-BB5A-6E442BA5630B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="3629025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7205,35 +6557,35 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
@@ -7274,18 +6626,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7301,7 +6653,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7315,7 +6667,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="54" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7326,8 +6678,8 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="66" t="s">
-        <v>112</v>
+      <c r="F8" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7335,7 +6687,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7344,8 +6696,8 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="67" t="s">
-        <v>113</v>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7353,7 +6705,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7362,14 +6714,14 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="65" t="s">
-        <v>19</v>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7379,41 +6731,37 @@
         <v>25</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="65" t="s">
-        <v>15</v>
-      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="20" t="s">
-        <v>114</v>
-      </c>
+      <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7427,7 +6775,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
+      <c r="A15" s="56"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7439,7 +6787,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="57" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7453,7 +6801,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
+      <c r="A17" s="56"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7465,7 +6813,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="57" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7485,7 +6833,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7503,14 +6851,12 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13" t="s">
         <v>15</v>
@@ -7521,12 +6867,10 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55"/>
+      <c r="A21" s="56"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
-      <c r="D21" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="21" t="s">
         <v>35</v>
@@ -7537,19 +6881,19 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="54" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="44" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="44" t="s">
         <v>37</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -7559,17 +6903,17 @@
       <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -7579,17 +6923,17 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="45" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="23"/>
@@ -7597,17 +6941,17 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="44" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="23"/>
@@ -7615,912 +6959,884 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="57" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="32" t="s">
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="56"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="31" t="s">
+      <c r="G29" s="29" t="s">
         <v>48</v>
       </c>
+      <c r="H29" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="64"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="33" t="s">
+      <c r="F30" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="31"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="G30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="55"/>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H31" s="31"/>
+      <c r="F31" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="54"/>
-      <c r="B33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>51</v>
+      <c r="A32" s="55"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="58"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="38" t="s">
+        <v>55</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" s="31" t="s">
-        <v>48</v>
-      </c>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="54"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="31"/>
+      <c r="A34" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="35" t="s">
-        <v>54</v>
-      </c>
+      <c r="C35" s="16"/>
       <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H35" s="29"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="15"/>
+      <c r="E35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17"/>
+      <c r="A37" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="51"/>
+        <v>59</v>
+      </c>
+      <c r="B38" s="50"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="55"/>
+      <c r="B40" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>20</v>
-      </c>
+      <c r="A41" s="55"/>
+      <c r="B41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="54"/>
-      <c r="B42" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>24</v>
+      <c r="A42" s="55"/>
+      <c r="B42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
-      <c r="B43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>61</v>
+      <c r="A43" s="55"/>
+      <c r="B43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>62</v>
+      <c r="A44" s="55"/>
+      <c r="B44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>64</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="54"/>
-      <c r="B45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="33" t="s">
-        <v>20</v>
+      <c r="A45" s="55"/>
+      <c r="B45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>62</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>63</v>
+      <c r="A46" s="55"/>
+      <c r="B46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="33" t="s">
-        <v>61</v>
+      <c r="A47" s="55"/>
+      <c r="B47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>64</v>
+      <c r="A48" s="55"/>
+      <c r="B48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>20</v>
-      </c>
+      <c r="A49" s="55"/>
+      <c r="B49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="31"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
-      <c r="B50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>65</v>
-      </c>
+      <c r="A50" s="55"/>
+      <c r="B50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="31"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="54"/>
-      <c r="B51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="30"/>
+      <c r="A51" s="55"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="31"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="18"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="54"/>
-      <c r="B52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="18"/>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="56"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="29"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="54"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="18"/>
+      <c r="A53" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="28"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
       <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="56" t="s">
-        <v>68</v>
+      <c r="A55" s="57" t="s">
+        <v>70</v>
       </c>
       <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
+      <c r="C55" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>54</v>
+      </c>
       <c r="E55" s="13"/>
       <c r="F55" s="14"/>
       <c r="G55" s="13"/>
       <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="55"/>
+      <c r="A56" s="56"/>
       <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
+      <c r="C56" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>72</v>
+      </c>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
       <c r="G56" s="16"/>
       <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="G57" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="55"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="17"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
-        <v>72</v>
-      </c>
+      <c r="A59" s="55"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="G59" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>15</v>
+      <c r="F59" s="1"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="42" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
+      <c r="A60" s="55"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>75</v>
+      <c r="G60" s="39"/>
+      <c r="H60" s="40" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="54"/>
+      <c r="A61" s="55"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="41" t="s">
-        <v>73</v>
+      <c r="G61" s="39"/>
+      <c r="H61" s="19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54"/>
+      <c r="A62" s="55"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="39" t="s">
-        <v>76</v>
+      <c r="G62" s="39"/>
+      <c r="H62" s="18" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="19" t="s">
+      <c r="G63" s="39"/>
+      <c r="H63" s="42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="56"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="49"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="42" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" s="46"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="48"/>
+      <c r="C66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="55"/>
+      <c r="B67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H67" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="13" t="s">
+      <c r="A68" s="55"/>
+      <c r="B68" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="56"/>
+      <c r="B69" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="30"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" s="50"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="52"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="15"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="55"/>
+      <c r="B72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="18"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="55"/>
+      <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
-      <c r="B69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G69" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H69" s="31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="54"/>
-      <c r="B70" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
-      <c r="B71" s="35" t="s">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="56"/>
+      <c r="B74" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="17"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H71" s="29"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="49"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="51"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="15"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="54"/>
-      <c r="B74" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="18"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="54"/>
-      <c r="B75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
-    </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G75" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="55"/>
-      <c r="B76" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="17"/>
+      <c r="B76" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="40" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>53</v>
-      </c>
+      <c r="A77" s="55"/>
+      <c r="B77" s="38"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="G77" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="54"/>
-      <c r="B78" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="54"/>
-      <c r="B79" s="37"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="2" t="s">
+      <c r="F77" s="1"/>
+      <c r="G77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="H77" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="56"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="52"/>
+    </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="55"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>89</v>
-      </c>
+      <c r="A80" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="50"/>
+      <c r="C80" s="51"/>
+      <c r="D80" s="51"/>
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+      <c r="G80" s="51"/>
+      <c r="H80" s="52"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="49"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="51"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B82" s="49"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="51"/>
+        <v>93</v>
+      </c>
+      <c r="B81" s="50"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="52"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="14"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B83" s="49"/>
-      <c r="C83" s="50"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="51"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="55"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="49"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="51"/>
-    </row>
-    <row r="87" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" s="50"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="52"/>
+    </row>
+    <row r="85" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="53"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -8534,28 +7850,28 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="A39:A52"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A59:A66"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A57:A64"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
     <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8574,36 +7890,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+      <c r="B4" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="B5" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8761,7 +8077,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8778,7 +8094,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8795,7 +8111,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8812,7 +8128,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8829,7 +8145,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8846,7 +8162,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8863,7 +8179,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8880,7 +8196,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8897,7 +8213,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8914,7 +8230,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8931,7 +8247,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8948,7 +8264,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8965,7 +8281,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8982,7 +8298,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8999,7 +8315,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9016,7 +8332,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9033,7 +8349,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9050,7 +8366,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9067,7 +8383,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9117,40 +8433,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36791057-EDBA-47EC-95E7-7280EFA45539}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0D84B53-0822-432C-9F95-5FD5DA8BE8BB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="118">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -367,6 +367,15 @@
   </si>
   <si>
     <t>09:00/16:00</t>
+  </si>
+  <si>
+    <t>STAGE // LEAGUES</t>
+  </si>
+  <si>
+    <t>STAGE // P100 // LEAGUES</t>
+  </si>
+  <si>
+    <t>STAGE // P25 // LEAGUES</t>
   </si>
 </sst>
 </file>
@@ -799,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -998,6 +1007,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7236,9 +7251,15 @@
       <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>117</v>
+      </c>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -7521,42 +7542,42 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="21" t="s">
+      <c r="E21" s="1"/>
+      <c r="F21" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17" t="s">
+      <c r="G21" s="1"/>
+      <c r="H21" s="18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="18"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="15"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="54"/>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0D84B53-0822-432C-9F95-5FD5DA8BE8BB}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{647677E5-C102-4B9E-B7F2-A87C09350046}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="119">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>STAGE // P25 // LEAGUES</t>
+  </si>
+  <si>
+    <t>FERIE // P250</t>
   </si>
 </sst>
 </file>
@@ -7260,8 +7263,12 @@
       <c r="D3" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+      <c r="E3" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>118</v>
+      </c>
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
     </row>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{647677E5-C102-4B9E-B7F2-A87C09350046}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E246A5A6-C552-47DF-81E6-CEED25C1E7F8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7226,7 +7226,7 @@
   <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="43.85546875" customWidth="1"/>
+    <col min="1" max="8" width="45.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8586,7 +8586,7 @@
     <mergeCell ref="B40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="36" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E246A5A6-C552-47DF-81E6-CEED25C1E7F8}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7D28D1-374A-491A-94D5-03DC69F67134}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="113">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -168,6 +168,9 @@
     <t>07:55/17:00</t>
   </si>
   <si>
+    <t>08:15/14:00</t>
+  </si>
+  <si>
     <t>09:00/19:00</t>
   </si>
   <si>
@@ -354,31 +357,10 @@
     <t>14/04/2026 16:04</t>
   </si>
   <si>
+    <t>09:00/17:30</t>
+  </si>
+  <si>
     <t>07:55/14:00</t>
-  </si>
-  <si>
-    <t>15:00/18:00</t>
-  </si>
-  <si>
-    <t>INVEN</t>
-  </si>
-  <si>
-    <t>06:00/07:30</t>
-  </si>
-  <si>
-    <t>09:00/16:00</t>
-  </si>
-  <si>
-    <t>STAGE // LEAGUES</t>
-  </si>
-  <si>
-    <t>STAGE // P100 // LEAGUES</t>
-  </si>
-  <si>
-    <t>STAGE // P25 // LEAGUES</t>
-  </si>
-  <si>
-    <t>FERIE // P250</t>
   </si>
 </sst>
 </file>
@@ -492,7 +474,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -534,14 +516,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -796,22 +772,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -890,6 +855,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1000,24 +968,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1397,6 +1347,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
@@ -2499,21 +2493,153 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2541,103 +2667,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2675,13 +2713,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2719,13 +2757,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2763,13 +2801,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2795,6 +2833,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2818,10 +2900,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2862,10 +2988,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2883,6 +3009,1062 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2906,10 +4088,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2939,21 +4121,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2981,516 +4163,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3511,566 +4209,38 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4094,10 +4264,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4115,94 +4285,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4226,10 +4308,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4257,23 +4339,243 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4301,67 +4603,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4389,67 +4647,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4477,32 +4735,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4523,21 +4781,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4565,155 +4823,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4741,76 +4955,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4831,21 +5133,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4875,197 +5177,65 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5093,32 +5263,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5139,21 +5441,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5181,172 +5483,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5370,10 +5540,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5391,6 +5561,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5414,10 +5628,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5445,67 +5659,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5546,10 +5716,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5577,84 +5747,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15103929" y="12314464"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5667,57 +5793,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15103929" y="12314464"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5975,6 +6057,94 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0D3522B-1460-4B06-A15B-6831EAAAB1B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15103929" y="1143000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDF2039-6A37-48FF-AE60-3E6609376C72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7551964" y="1143000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6006,842 +6176,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10069286" y="762000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C4E0D82-F8FE-49F6-BBB1-FCA34AE6B9DD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F62859C-F136-4142-9731-F5C10BBDE096}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CE02145-BF9F-4959-BECC-56E863A9381B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7974EDE5-CEB5-456A-A2EE-6E0C148C713E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE7641C-186C-4AD1-9628-59490CFBAFE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3746426-C2AE-4C70-8D61-5EC2073BDDD0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B47883-26F3-4071-8B26-A0E4FCE209F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86860902-EEA3-4EF1-BC72-9D15FDB5CA7C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD5157ED-8C59-4198-933D-F108F02B419C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EC240F8-4C3B-44F5-AD04-FA9E2A88F91F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="130" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8039DC6-825D-422B-8B85-6572530FC6BF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="131" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8DA95EA-A40E-4F86-ABFA-ABA2228F4786}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="132" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EA90DC-F1A4-4E9B-8A32-F437ADF667D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="133" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C34D350-395B-40E2-B462-0B25CC5D1E09}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="134" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C23EDF8-EE02-4C1C-A010-303C5F5C5A4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11702143" y="16178893"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="135" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{355868F0-8922-4754-BD84-F93D4DDB73DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5851071" y="13035643"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="136" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{032F124A-F13E-4A50-A618-95C926A42538}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="2867025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="137" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD0ED26-4249-4AD5-AC50-52F58791D4D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="3248025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="138" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8078E310-A965-4F05-BB5A-6E442BA5630B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="3629025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7223,52 +6557,42 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="45.140625" customWidth="1"/>
+    <col min="1" max="8" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>118</v>
-      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
     </row>
@@ -7302,18 +6626,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7329,7 +6653,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7343,7 +6667,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="54" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7354,8 +6678,8 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="66" t="s">
-        <v>112</v>
+      <c r="F8" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7363,7 +6687,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7372,8 +6696,8 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="67" t="s">
-        <v>113</v>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7381,7 +6705,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7390,14 +6714,14 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="65" t="s">
-        <v>19</v>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7407,41 +6731,37 @@
         <v>25</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="65" t="s">
-        <v>15</v>
-      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="20" t="s">
-        <v>114</v>
-      </c>
+      <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7455,7 +6775,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
+      <c r="A15" s="56"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7467,7 +6787,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="57" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7481,7 +6801,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
+      <c r="A17" s="56"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7493,7 +6813,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="57" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7513,7 +6833,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7531,14 +6851,12 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13" t="s">
         <v>15</v>
@@ -7549,55 +6867,53 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="57"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="20" t="s">
+      <c r="A21" s="56"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="18" t="s">
+      <c r="G21" s="16"/>
+      <c r="H21" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="68" t="s">
+      <c r="E22" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="69" t="s">
+      <c r="F22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="15"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -7607,17 +6923,17 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="45" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="23"/>
@@ -7625,17 +6941,17 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="44" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="23"/>
@@ -7643,912 +6959,884 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="57" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="32" t="s">
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="56"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="31" t="s">
+      <c r="G29" s="29" t="s">
         <v>48</v>
       </c>
+      <c r="H29" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="64"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="33" t="s">
+      <c r="F30" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="31"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="G30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="55"/>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H31" s="31"/>
+      <c r="F31" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="54"/>
-      <c r="B33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>51</v>
+      <c r="A32" s="55"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="58"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="38" t="s">
+        <v>55</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" s="31" t="s">
-        <v>48</v>
-      </c>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="54"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="31"/>
+      <c r="A34" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="35" t="s">
-        <v>54</v>
-      </c>
+      <c r="C35" s="16"/>
       <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H35" s="29"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="15"/>
+      <c r="E35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17"/>
+      <c r="A37" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="51"/>
+        <v>59</v>
+      </c>
+      <c r="B38" s="50"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="55"/>
+      <c r="B40" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>20</v>
-      </c>
+      <c r="A41" s="55"/>
+      <c r="B41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="54"/>
-      <c r="B42" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>24</v>
+      <c r="A42" s="55"/>
+      <c r="B42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
-      <c r="B43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>61</v>
+      <c r="A43" s="55"/>
+      <c r="B43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>62</v>
+      <c r="A44" s="55"/>
+      <c r="B44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>64</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="54"/>
-      <c r="B45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="33" t="s">
-        <v>20</v>
+      <c r="A45" s="55"/>
+      <c r="B45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>62</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>63</v>
+      <c r="A46" s="55"/>
+      <c r="B46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="33" t="s">
-        <v>61</v>
+      <c r="A47" s="55"/>
+      <c r="B47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>64</v>
+      <c r="A48" s="55"/>
+      <c r="B48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>20</v>
-      </c>
+      <c r="A49" s="55"/>
+      <c r="B49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="31"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
-      <c r="B50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>65</v>
-      </c>
+      <c r="A50" s="55"/>
+      <c r="B50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="31"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="54"/>
-      <c r="B51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="30"/>
+      <c r="A51" s="55"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="31"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="18"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="54"/>
-      <c r="B52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="18"/>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="56"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="29"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="54"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="18"/>
+      <c r="A53" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="28"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
       <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="56" t="s">
-        <v>68</v>
+      <c r="A55" s="57" t="s">
+        <v>70</v>
       </c>
       <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
+      <c r="C55" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>54</v>
+      </c>
       <c r="E55" s="13"/>
       <c r="F55" s="14"/>
       <c r="G55" s="13"/>
       <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="55"/>
+      <c r="A56" s="56"/>
       <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
+      <c r="C56" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>72</v>
+      </c>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
       <c r="G56" s="16"/>
       <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="G57" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="55"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="17"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
-        <v>72</v>
-      </c>
+      <c r="A59" s="55"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="G59" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>15</v>
+      <c r="F59" s="1"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="42" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
+      <c r="A60" s="55"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>75</v>
+      <c r="G60" s="39"/>
+      <c r="H60" s="40" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="54"/>
+      <c r="A61" s="55"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="41" t="s">
-        <v>73</v>
+      <c r="G61" s="39"/>
+      <c r="H61" s="19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54"/>
+      <c r="A62" s="55"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="39" t="s">
-        <v>76</v>
+      <c r="G62" s="39"/>
+      <c r="H62" s="18" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="19" t="s">
+      <c r="G63" s="39"/>
+      <c r="H63" s="42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="56"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="49"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="42" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" s="46"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="48"/>
+      <c r="C66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="55"/>
+      <c r="B67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H67" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="13" t="s">
+      <c r="A68" s="55"/>
+      <c r="B68" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="56"/>
+      <c r="B69" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="30"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" s="50"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="52"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="15"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="55"/>
+      <c r="B72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="18"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="55"/>
+      <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
-      <c r="B69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G69" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H69" s="31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="54"/>
-      <c r="B70" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
-      <c r="B71" s="35" t="s">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="56"/>
+      <c r="B74" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="17"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H71" s="29"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="49"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="51"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="15"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="54"/>
-      <c r="B74" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="18"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="54"/>
-      <c r="B75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
-    </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G75" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="55"/>
-      <c r="B76" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="17"/>
+      <c r="B76" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="40" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>53</v>
-      </c>
+      <c r="A77" s="55"/>
+      <c r="B77" s="38"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="G77" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="54"/>
-      <c r="B78" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="54"/>
-      <c r="B79" s="37"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="2" t="s">
+      <c r="F77" s="1"/>
+      <c r="G77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="H77" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="56"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="52"/>
+    </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="55"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>89</v>
-      </c>
+      <c r="A80" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="50"/>
+      <c r="C80" s="51"/>
+      <c r="D80" s="51"/>
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+      <c r="G80" s="51"/>
+      <c r="H80" s="52"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="49"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="51"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B82" s="49"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="51"/>
+        <v>93</v>
+      </c>
+      <c r="B81" s="50"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="52"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="14"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B83" s="49"/>
-      <c r="C83" s="50"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="51"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="55"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="49"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="51"/>
-    </row>
-    <row r="87" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" s="50"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="52"/>
+    </row>
+    <row r="85" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="53"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -8562,31 +7850,31 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="A39:A52"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A59:A66"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A57:A64"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
     <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="36" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8602,36 +7890,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+      <c r="B4" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="B5" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8789,7 +8077,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8806,7 +8094,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8823,7 +8111,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8840,7 +8128,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8857,7 +8145,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8874,7 +8162,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8891,7 +8179,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8908,7 +8196,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8925,7 +8213,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8942,7 +8230,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8959,7 +8247,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8976,7 +8264,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8993,7 +8281,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -9010,7 +8298,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -9027,7 +8315,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9044,7 +8332,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9061,7 +8349,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9078,7 +8366,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9095,7 +8383,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9145,40 +8433,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E246A5A6-C552-47DF-81E6-CEED25C1E7F8}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F6559A-3D48-4A54-9F67-D6CECA8A863A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="120">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -378,7 +378,10 @@
     <t>STAGE // P25 // LEAGUES</t>
   </si>
   <si>
-    <t>FERIE // P250</t>
+    <t>FERIE // P250 // CUP France 26</t>
+  </si>
+  <si>
+    <t>CUP France 26 // ANNIV</t>
   </si>
 </sst>
 </file>
@@ -7269,8 +7272,12 @@
       <c r="F3" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
+      <c r="G3" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F6559A-3D48-4A54-9F67-D6CECA8A863A}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA7D28D1-374A-491A-94D5-03DC69F67134}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="113">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -168,6 +168,9 @@
     <t>07:55/17:00</t>
   </si>
   <si>
+    <t>08:15/14:00</t>
+  </si>
+  <si>
     <t>09:00/19:00</t>
   </si>
   <si>
@@ -354,34 +357,10 @@
     <t>14/04/2026 16:04</t>
   </si>
   <si>
+    <t>09:00/17:30</t>
+  </si>
+  <si>
     <t>07:55/14:00</t>
-  </si>
-  <si>
-    <t>15:00/18:00</t>
-  </si>
-  <si>
-    <t>INVEN</t>
-  </si>
-  <si>
-    <t>06:00/07:30</t>
-  </si>
-  <si>
-    <t>09:00/16:00</t>
-  </si>
-  <si>
-    <t>STAGE // LEAGUES</t>
-  </si>
-  <si>
-    <t>STAGE // P100 // LEAGUES</t>
-  </si>
-  <si>
-    <t>STAGE // P25 // LEAGUES</t>
-  </si>
-  <si>
-    <t>FERIE // P250 // CUP France 26</t>
-  </si>
-  <si>
-    <t>CUP France 26 // ANNIV</t>
   </si>
 </sst>
 </file>
@@ -495,7 +474,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -537,14 +516,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -799,22 +772,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -893,6 +855,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1003,24 +968,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1400,6 +1347,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
@@ -2502,21 +2493,153 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2544,103 +2667,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2678,13 +2713,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2722,13 +2757,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2766,13 +2801,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2798,6 +2833,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2821,10 +2900,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2865,10 +2988,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2886,6 +3009,1062 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2909,10 +4088,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2942,21 +4121,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2984,516 +4163,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3514,566 +4209,38 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4097,10 +4264,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4118,94 +4285,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4229,10 +4308,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4260,23 +4339,243 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4304,67 +4603,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4392,67 +4647,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4480,32 +4735,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4526,21 +4781,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4568,155 +4823,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4744,76 +4955,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4834,21 +5133,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4878,197 +5177,65 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5096,32 +5263,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5142,21 +5441,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5184,172 +5483,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5373,10 +5540,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5394,6 +5561,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5417,10 +5628,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5448,67 +5659,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5549,10 +5716,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5580,84 +5747,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15103929" y="12314464"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5670,57 +5793,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F54055-D9A1-42F2-A9A4-B4636296740C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15103929" y="12314464"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5978,6 +6057,94 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0D3522B-1460-4B06-A15B-6831EAAAB1B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15103929" y="1143000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDF2039-6A37-48FF-AE60-3E6609376C72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7551964" y="1143000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6009,842 +6176,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10069286" y="762000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C4E0D82-F8FE-49F6-BBB1-FCA34AE6B9DD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F62859C-F136-4142-9731-F5C10BBDE096}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="5660571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CE02145-BF9F-4959-BECC-56E863A9381B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7974EDE5-CEB5-456A-A2EE-6E0C148C713E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE7641C-186C-4AD1-9628-59490CFBAFE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3746426-C2AE-4C70-8D61-5EC2073BDDD0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B47883-26F3-4071-8B26-A0E4FCE209F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86860902-EEA3-4EF1-BC72-9D15FDB5CA7C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD5157ED-8C59-4198-933D-F108F02B419C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EC240F8-4C3B-44F5-AD04-FA9E2A88F91F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="130" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8039DC6-825D-422B-8B85-6572530FC6BF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20478750" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="131" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8DA95EA-A40E-4F86-ABFA-ABA2228F4786}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14627679" y="6041571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="132" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10EA90DC-F1A4-4E9B-8A32-F437ADF667D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="133" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C34D350-395B-40E2-B462-0B25CC5D1E09}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17553214" y="6422571"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="134" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C23EDF8-EE02-4C1C-A010-303C5F5C5A4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11702143" y="16178893"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="135" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{355868F0-8922-4754-BD84-F93D4DDB73DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5851071" y="13035643"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="136" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{032F124A-F13E-4A50-A618-95C926A42538}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="2867025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="137" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD0ED26-4249-4AD5-AC50-52F58791D4D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="3248025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="138" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8078E310-A965-4F05-BB5A-6E442BA5630B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="3629025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7226,58 +6557,44 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="45.140625" customWidth="1"/>
+    <col min="1" max="8" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>119</v>
-      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
@@ -7309,18 +6626,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7336,7 +6653,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7350,7 +6667,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="54" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7361,8 +6678,8 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="66" t="s">
-        <v>112</v>
+      <c r="F8" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7370,7 +6687,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7379,8 +6696,8 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="67" t="s">
-        <v>113</v>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7388,7 +6705,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7397,14 +6714,14 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="65" t="s">
-        <v>19</v>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7414,41 +6731,37 @@
         <v>25</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="65" t="s">
-        <v>15</v>
-      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="20" t="s">
-        <v>114</v>
-      </c>
+      <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7462,7 +6775,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
+      <c r="A15" s="56"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7474,7 +6787,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="57" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7488,7 +6801,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
+      <c r="A17" s="56"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7500,7 +6813,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="57" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7520,7 +6833,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7538,14 +6851,12 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13" t="s">
         <v>15</v>
@@ -7556,55 +6867,53 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="57"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="20" t="s">
+      <c r="A21" s="56"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="18" t="s">
+      <c r="G21" s="16"/>
+      <c r="H21" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="68" t="s">
+      <c r="E22" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="69" t="s">
+      <c r="F22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="15"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="44" t="s">
         <v>40</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -7614,17 +6923,17 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="45" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="23"/>
@@ -7632,17 +6941,17 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="44" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="23"/>
@@ -7650,912 +6959,884 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="57" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="32" t="s">
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="56"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="31" t="s">
+      <c r="G29" s="29" t="s">
         <v>48</v>
       </c>
+      <c r="H29" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="64"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="33" t="s">
+      <c r="F30" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="31"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="G30" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="55"/>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H31" s="31"/>
+      <c r="F31" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="54"/>
-      <c r="B33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>51</v>
+      <c r="A32" s="55"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="58"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="38" t="s">
+        <v>55</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" s="31" t="s">
-        <v>48</v>
-      </c>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="54"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="31"/>
+      <c r="A34" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="35" t="s">
-        <v>54</v>
-      </c>
+      <c r="C35" s="16"/>
       <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H35" s="29"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="15"/>
+      <c r="E35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="50"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17"/>
+      <c r="A37" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="51"/>
+        <v>59</v>
+      </c>
+      <c r="B38" s="50"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="55"/>
+      <c r="B40" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>20</v>
-      </c>
+      <c r="A41" s="55"/>
+      <c r="B41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="54"/>
-      <c r="B42" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>24</v>
+      <c r="A42" s="55"/>
+      <c r="B42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
-      <c r="B43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>61</v>
+      <c r="A43" s="55"/>
+      <c r="B43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>62</v>
+      <c r="A44" s="55"/>
+      <c r="B44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>64</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="54"/>
-      <c r="B45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="33" t="s">
-        <v>20</v>
+      <c r="A45" s="55"/>
+      <c r="B45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>62</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>63</v>
+      <c r="A46" s="55"/>
+      <c r="B46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="33" t="s">
-        <v>61</v>
+      <c r="A47" s="55"/>
+      <c r="B47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>64</v>
+      <c r="A48" s="55"/>
+      <c r="B48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
-      <c r="B49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>20</v>
-      </c>
+      <c r="A49" s="55"/>
+      <c r="B49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="31"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
-      <c r="B50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>65</v>
-      </c>
+      <c r="A50" s="55"/>
+      <c r="B50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="31"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="54"/>
-      <c r="B51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="30"/>
+      <c r="A51" s="55"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="31"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="18"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="54"/>
-      <c r="B52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="18"/>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="56"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="29"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="54"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="18"/>
+      <c r="A53" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="28"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="16"/>
       <c r="G54" s="16"/>
       <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="56" t="s">
-        <v>68</v>
+      <c r="A55" s="57" t="s">
+        <v>70</v>
       </c>
       <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
+      <c r="C55" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>54</v>
+      </c>
       <c r="E55" s="13"/>
       <c r="F55" s="14"/>
       <c r="G55" s="13"/>
       <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="55"/>
+      <c r="A56" s="56"/>
       <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
+      <c r="C56" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>72</v>
+      </c>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
       <c r="G56" s="16"/>
       <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="G57" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="55"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="17"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
-        <v>72</v>
-      </c>
+      <c r="A59" s="55"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="G59" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>15</v>
+      <c r="F59" s="1"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="42" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
+      <c r="A60" s="55"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>75</v>
+      <c r="G60" s="39"/>
+      <c r="H60" s="40" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="54"/>
+      <c r="A61" s="55"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="41" t="s">
-        <v>73</v>
+      <c r="G61" s="39"/>
+      <c r="H61" s="19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54"/>
+      <c r="A62" s="55"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="39" t="s">
-        <v>76</v>
+      <c r="G62" s="39"/>
+      <c r="H62" s="18" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="19" t="s">
+      <c r="G63" s="39"/>
+      <c r="H63" s="42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="56"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="49"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="42" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" s="46"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="48"/>
+      <c r="C66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="55"/>
+      <c r="B67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H67" s="32" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="13" t="s">
+      <c r="A68" s="55"/>
+      <c r="B68" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="56"/>
+      <c r="B69" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="30"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" s="50"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="52"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="15"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="55"/>
+      <c r="B72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="18"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="55"/>
+      <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
-      <c r="B69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G69" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H69" s="31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="54"/>
-      <c r="B70" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
-      <c r="B71" s="35" t="s">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="56"/>
+      <c r="B74" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="17"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H71" s="29"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="49"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="51"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="15"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="54"/>
-      <c r="B74" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="18"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="54"/>
-      <c r="B75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
-    </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G75" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="55"/>
-      <c r="B76" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="17"/>
+      <c r="B76" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="40" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>53</v>
-      </c>
+      <c r="A77" s="55"/>
+      <c r="B77" s="38"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="G77" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="54"/>
-      <c r="B78" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="54"/>
-      <c r="B79" s="37"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="2" t="s">
+      <c r="F77" s="1"/>
+      <c r="G77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="H77" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="56"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="52"/>
+    </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="55"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>89</v>
-      </c>
+      <c r="A80" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="50"/>
+      <c r="C80" s="51"/>
+      <c r="D80" s="51"/>
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+      <c r="G80" s="51"/>
+      <c r="H80" s="52"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="49"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="51"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B82" s="49"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="51"/>
+        <v>93</v>
+      </c>
+      <c r="B81" s="50"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="52"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="14"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B83" s="49"/>
-      <c r="C83" s="50"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="51"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="55"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="49"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="51"/>
-    </row>
-    <row r="87" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" s="50"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="52"/>
+    </row>
+    <row r="85" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="53"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -8569,31 +7850,31 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="A39:A52"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A59:A66"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A57:A64"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
     <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="36" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8609,36 +7890,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+      <c r="B4" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="B5" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8796,7 +8077,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8813,7 +8094,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8830,7 +8111,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8847,7 +8128,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8864,7 +8145,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8881,7 +8162,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8898,7 +8179,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8915,7 +8196,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8932,7 +8213,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8949,7 +8230,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8966,7 +8247,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8983,7 +8264,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -9000,7 +8281,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -9017,7 +8298,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -9034,7 +8315,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9051,7 +8332,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9068,7 +8349,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9085,7 +8366,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9102,7 +8383,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9152,40 +8433,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F6559A-3D48-4A54-9F67-D6CECA8A863A}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{933C02E7-051B-423C-958D-FE7F79FD3481}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="120">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -2865,10 +2865,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2909,10 +2909,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2930,6 +2930,1062 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2953,10 +4009,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2984,1079 +4040,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4084,23 +4084,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4128,111 +4216,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4260,23 +4260,243 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4304,67 +4524,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4392,67 +4568,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4462,50 +4638,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4537,10 +4669,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4568,120 +4700,76 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4702,21 +4790,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4744,76 +4832,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4845,10 +5021,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4878,162 +5054,30 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5054,21 +5098,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5096,32 +5140,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5142,21 +5318,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5174,182 +5350,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5373,10 +5373,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5417,10 +5417,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5438,6 +5438,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5461,10 +5505,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5492,23 +5536,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5538,21 +5582,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5580,103 +5624,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6374,13 +6330,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6418,13 +6374,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6462,13 +6418,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6506,13 +6462,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6550,13 +6506,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6594,13 +6550,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6638,13 +6594,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7226,10 +7182,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="45.140625" customWidth="1"/>
+    <col min="1" max="8" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7829,7 +7785,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B38" s="49"/>
       <c r="C38" s="50"/>
@@ -7841,7 +7797,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B39" s="49"/>
       <c r="C39" s="50"/>
@@ -7851,50 +7807,56 @@
       <c r="G39" s="50"/>
       <c r="H39" s="51"/>
     </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="51"/>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
-        <v>59</v>
-      </c>
+      <c r="A41" s="54"/>
       <c r="B41" s="30" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E41" s="30" t="s">
-        <v>20</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="54"/>
-      <c r="B42" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>24</v>
+      <c r="B42" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -7902,17 +7864,17 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="54"/>
-      <c r="B43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>61</v>
+      <c r="B43" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -7920,17 +7882,17 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="54"/>
-      <c r="B44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>62</v>
+      <c r="B44" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>20</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -7938,17 +7900,17 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="54"/>
-      <c r="B45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="33" t="s">
-        <v>20</v>
+      <c r="B45" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>63</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -7956,17 +7918,17 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="54"/>
-      <c r="B46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>63</v>
+      <c r="B46" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -7974,17 +7936,17 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="54"/>
-      <c r="B47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="33" t="s">
-        <v>61</v>
+      <c r="B47" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>64</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -7992,17 +7954,17 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="54"/>
-      <c r="B48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>64</v>
+      <c r="B48" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>20</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -8010,17 +7972,17 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="54"/>
-      <c r="B49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>20</v>
+      <c r="B49" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E49" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -8028,32 +7990,30 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="54"/>
-      <c r="B50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>65</v>
-      </c>
+      <c r="B50" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="30"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="54"/>
-      <c r="B51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>61</v>
+      <c r="B51" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>66</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="1"/>
@@ -8062,109 +8022,107 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="54"/>
-      <c r="B52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>66</v>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="33" t="s">
+        <v>20</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="18"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="54"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="18"/>
-    </row>
-    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28" t="s">
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="55"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E54" s="28"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="17"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="56" t="s">
+      <c r="E53" s="28"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="17"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="15"/>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="55"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="17"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="56" t="s">
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="15"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="55"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="17"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="34" t="s">
+      <c r="B56" s="13"/>
+      <c r="C56" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D56" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="55"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="35" t="s">
+      <c r="E56" s="13"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="15"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="55"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D57" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="17"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="17"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="G58" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
-        <v>72</v>
-      </c>
+      <c r="A59" s="54"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
       <c r="G59" s="38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -8174,11 +8132,9 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>75</v>
+      <c r="G60" s="38"/>
+      <c r="H60" s="41" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -8189,8 +8145,8 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="38"/>
-      <c r="H61" s="41" t="s">
-        <v>73</v>
+      <c r="H61" s="39" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -8201,8 +8157,8 @@
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="38"/>
-      <c r="H62" s="39" t="s">
-        <v>76</v>
+      <c r="H62" s="19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -8213,8 +8169,8 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="38"/>
-      <c r="H63" s="19" t="s">
-        <v>15</v>
+      <c r="H63" s="18" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -8225,151 +8181,153 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="38"/>
-      <c r="H64" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="41" t="s">
+      <c r="H64" s="41" t="s">
         <v>73</v>
       </c>
     </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="55"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="42" t="s">
+        <v>78</v>
+      </c>
+    </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="42" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
+      <c r="A66" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B67" s="46"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="48"/>
+      <c r="B66" s="46"/>
+      <c r="C66" s="47"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="47"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="48"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" s="27" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" s="27" t="s">
-        <v>19</v>
+      <c r="A68" s="54"/>
+      <c r="B68" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="G68" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="H68" s="31" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="54"/>
-      <c r="B69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="B69" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G69" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H69" s="31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="54"/>
-      <c r="B70" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="33" t="s">
+      <c r="F69" s="30"/>
+      <c r="G69" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H70" s="31"/>
+      <c r="H69" s="31"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="55"/>
+      <c r="B70" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="H70" s="29"/>
     </row>
     <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
-      <c r="B71" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H71" s="29"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="s">
+      <c r="A71" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="49"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="51"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="51"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="15"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="15"/>
+      <c r="A73" s="54"/>
+      <c r="B73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="54"/>
-      <c r="B74" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>24</v>
+      <c r="B74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -8377,98 +8335,96 @@
       <c r="G74" s="1"/>
       <c r="H74" s="18"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="54"/>
-      <c r="B75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
-    </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="55"/>
-      <c r="B76" s="16" t="s">
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="55"/>
+      <c r="B75" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C75" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="17"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="17"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="G76" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" s="39" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="53" t="s">
-        <v>86</v>
-      </c>
+      <c r="A77" s="54"/>
       <c r="B77" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
       <c r="G77" s="38" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="54"/>
-      <c r="B78" s="37" t="s">
-        <v>54</v>
-      </c>
+      <c r="B78" s="37"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="54"/>
-      <c r="B79" s="37"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="2" t="s">
+      <c r="G78" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="H78" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="55"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="55"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>89</v>
-      </c>
+      <c r="A80" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="49"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="51"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B81" s="49"/>
       <c r="C81" s="50"/>
@@ -8480,7 +8436,7 @@
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B82" s="49"/>
       <c r="C82" s="50"/>
@@ -8490,75 +8446,63 @@
       <c r="G82" s="50"/>
       <c r="H82" s="51"/>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B83" s="49"/>
-      <c r="C83" s="50"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="51"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="56" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13" t="s">
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E84" s="13" t="s">
+      <c r="E83" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="15" t="s">
+      <c r="F83" s="14"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="15" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="55"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="55"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+      <c r="A85" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="49"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="51"/>
-    </row>
-    <row r="87" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="50"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="51"/>
+    </row>
+    <row r="86" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="31">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:H1"/>
@@ -8569,31 +8513,30 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A41:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A40:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A59:A66"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A58:A65"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B80:H80"/>
     <mergeCell ref="B81:H81"/>
     <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B71:H71"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="36" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{933C02E7-051B-423C-958D-FE7F79FD3481}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{817EA6FF-035E-474F-92CD-FFD112723A35}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7185,7 +7185,7 @@
   <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="44.28515625" customWidth="1"/>
+    <col min="1" max="8" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8492,7 +8492,7 @@
       <c r="G85" s="50"/>
       <c r="H85" s="51"/>
     </row>
-    <row r="86" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="52"/>
       <c r="C86" s="52"/>
       <c r="D86" s="52"/>
@@ -8536,7 +8536,7 @@
     <mergeCell ref="B39:H39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="36" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{817EA6FF-035E-474F-92CD-FFD112723A35}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF97EFE7-7996-45EC-B71C-D43E8CBB8AEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Informations" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -949,63 +950,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1019,6 +963,63 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7189,28 +7190,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
@@ -7265,18 +7266,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="52" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7292,7 +7293,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7306,7 +7307,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="57" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7317,7 +7318,7 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="47" t="s">
         <v>112</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -7326,7 +7327,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7335,7 +7336,7 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="67" t="s">
+      <c r="F9" s="48" t="s">
         <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -7344,7 +7345,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7353,14 +7354,14 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="65" t="s">
+      <c r="F10" s="46" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
+      <c r="A11" s="58"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7376,21 +7377,21 @@
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
+      <c r="A12" s="58"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="65" t="s">
+      <c r="F12" s="46" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
@@ -7404,7 +7405,7 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="52" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7418,7 +7419,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7430,7 +7431,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="52" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7444,7 +7445,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7456,7 +7457,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="52" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7476,7 +7477,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7494,7 +7495,7 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="52" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="13"/>
@@ -7512,7 +7513,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="57"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
@@ -7528,29 +7529,29 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="52" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="68" t="s">
+      <c r="E22" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="69" t="s">
+      <c r="F22" s="50" t="s">
         <v>38</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
@@ -7570,7 +7571,7 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="25" t="s">
         <v>38</v>
       </c>
@@ -7588,7 +7589,7 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="23" t="s">
         <v>42</v>
       </c>
@@ -7606,7 +7607,7 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
@@ -7618,7 +7619,7 @@
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="16" t="s">
         <v>45</v>
       </c>
@@ -7630,7 +7631,7 @@
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="52" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="13"/>
@@ -7648,7 +7649,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
+      <c r="A29" s="60"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -7664,7 +7665,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="64"/>
+      <c r="A30" s="60"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -7676,7 +7677,7 @@
       <c r="H30" s="31"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
+      <c r="A31" s="59"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -7688,7 +7689,7 @@
       <c r="H31" s="31"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -7710,7 +7711,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="54"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="1" t="s">
         <v>50</v>
       </c>
@@ -7730,7 +7731,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="54"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="1"/>
       <c r="C34" s="36" t="s">
         <v>53</v>
@@ -7744,7 +7745,7 @@
       <c r="H34" s="31"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
+      <c r="A35" s="53"/>
       <c r="B35" s="16"/>
       <c r="C35" s="35" t="s">
         <v>54</v>
@@ -7758,7 +7759,7 @@
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="52" t="s">
         <v>55</v>
       </c>
       <c r="B36" s="13"/>
@@ -7772,7 +7773,7 @@
       <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="55"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -7787,28 +7788,28 @@
       <c r="A38" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
+      <c r="B38" s="62"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="64"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
+      <c r="B39" s="62"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="64"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="57" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="30" t="s">
@@ -7827,7 +7828,7 @@
       <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="54"/>
+      <c r="A41" s="58"/>
       <c r="B41" s="30" t="s">
         <v>60</v>
       </c>
@@ -7845,7 +7846,7 @@
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="54"/>
+      <c r="A42" s="58"/>
       <c r="B42" s="33" t="s">
         <v>61</v>
       </c>
@@ -7863,7 +7864,7 @@
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
+      <c r="A43" s="58"/>
       <c r="B43" s="30" t="s">
         <v>62</v>
       </c>
@@ -7881,7 +7882,7 @@
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
+      <c r="A44" s="58"/>
       <c r="B44" s="33" t="s">
         <v>20</v>
       </c>
@@ -7899,7 +7900,7 @@
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="54"/>
+      <c r="A45" s="58"/>
       <c r="B45" s="30" t="s">
         <v>63</v>
       </c>
@@ -7917,7 +7918,7 @@
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
+      <c r="A46" s="58"/>
       <c r="B46" s="33" t="s">
         <v>61</v>
       </c>
@@ -7935,7 +7936,7 @@
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="30" t="s">
         <v>64</v>
       </c>
@@ -7953,7 +7954,7 @@
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="33" t="s">
         <v>20</v>
       </c>
@@ -7971,7 +7972,7 @@
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="54"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="30" t="s">
         <v>65</v>
       </c>
@@ -7989,7 +7990,7 @@
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="54"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="33" t="s">
         <v>61</v>
       </c>
@@ -8005,7 +8006,7 @@
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="54"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="30" t="s">
         <v>66</v>
       </c>
@@ -8021,7 +8022,7 @@
       <c r="H51" s="18"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="54"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="33" t="s">
@@ -8033,7 +8034,7 @@
       <c r="H52" s="18"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="55"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28" t="s">
@@ -8045,7 +8046,7 @@
       <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="56" t="s">
+      <c r="A54" s="52" t="s">
         <v>68</v>
       </c>
       <c r="B54" s="13"/>
@@ -8057,7 +8058,7 @@
       <c r="H54" s="15"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="55"/>
+      <c r="A55" s="53"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -8067,7 +8068,7 @@
       <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="52" t="s">
         <v>69</v>
       </c>
       <c r="B56" s="13"/>
@@ -8083,7 +8084,7 @@
       <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="55"/>
+      <c r="A57" s="53"/>
       <c r="B57" s="16"/>
       <c r="C57" s="35" t="s">
         <v>70</v>
@@ -8097,7 +8098,7 @@
       <c r="H57" s="17"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="53" t="s">
+      <c r="A58" s="57" t="s">
         <v>72</v>
       </c>
       <c r="B58" s="1"/>
@@ -8112,7 +8113,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="54"/>
+      <c r="A59" s="58"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -8126,7 +8127,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
+      <c r="A60" s="58"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -8138,7 +8139,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="54"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -8150,7 +8151,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54"/>
+      <c r="A62" s="58"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -8162,7 +8163,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
+      <c r="A63" s="58"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -8174,7 +8175,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
+      <c r="A64" s="58"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -8186,7 +8187,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="55"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
@@ -8201,16 +8202,16 @@
       <c r="A66" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B66" s="46"/>
-      <c r="C66" s="47"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="47"/>
-      <c r="F66" s="47"/>
-      <c r="G66" s="47"/>
-      <c r="H66" s="48"/>
+      <c r="B66" s="65"/>
+      <c r="C66" s="66"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="67"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="56" t="s">
+      <c r="A67" s="52" t="s">
         <v>80</v>
       </c>
       <c r="B67" s="13" t="s">
@@ -8232,7 +8233,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="54"/>
+      <c r="A68" s="58"/>
       <c r="B68" s="1" t="s">
         <v>81</v>
       </c>
@@ -8252,7 +8253,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
+      <c r="A69" s="58"/>
       <c r="B69" s="36" t="s">
         <v>53</v>
       </c>
@@ -8266,9 +8267,9 @@
       <c r="H69" s="31"/>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="55"/>
+      <c r="A70" s="53"/>
       <c r="B70" s="35" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
@@ -8283,16 +8284,16 @@
       <c r="A71" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B71" s="49"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="51"/>
+      <c r="B71" s="62"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="64"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="56" t="s">
+      <c r="A72" s="52" t="s">
         <v>83</v>
       </c>
       <c r="B72" s="13" t="s">
@@ -8308,7 +8309,7 @@
       <c r="H72" s="15"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="54"/>
+      <c r="A73" s="58"/>
       <c r="B73" s="1" t="s">
         <v>84</v>
       </c>
@@ -8322,7 +8323,7 @@
       <c r="H73" s="18"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="54"/>
+      <c r="A74" s="58"/>
       <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
@@ -8336,7 +8337,7 @@
       <c r="H74" s="18"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="55"/>
+      <c r="A75" s="53"/>
       <c r="B75" s="16" t="s">
         <v>85</v>
       </c>
@@ -8350,7 +8351,7 @@
       <c r="H75" s="17"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="53" t="s">
+      <c r="A76" s="57" t="s">
         <v>86</v>
       </c>
       <c r="B76" s="37" t="s">
@@ -8367,7 +8368,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="54"/>
+      <c r="A77" s="58"/>
       <c r="B77" s="37" t="s">
         <v>54</v>
       </c>
@@ -8383,7 +8384,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="54"/>
+      <c r="A78" s="58"/>
       <c r="B78" s="37"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -8397,7 +8398,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="55"/>
+      <c r="A79" s="53"/>
       <c r="B79" s="35"/>
       <c r="C79" s="16"/>
       <c r="D79" s="16"/>
@@ -8414,40 +8415,40 @@
       <c r="A80" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B80" s="49"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="51"/>
+      <c r="B80" s="62"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="64"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B81" s="49"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="51"/>
+      <c r="B81" s="62"/>
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="64"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B82" s="49"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="51"/>
+      <c r="B82" s="62"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="64"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="56" t="s">
+      <c r="A83" s="52" t="s">
         <v>93</v>
       </c>
       <c r="B83" s="13"/>
@@ -8465,7 +8466,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="55"/>
+      <c r="A84" s="53"/>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
       <c r="D84" s="16" t="s">
@@ -8484,35 +8485,39 @@
       <c r="A85" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="49"/>
-      <c r="C85" s="50"/>
-      <c r="D85" s="50"/>
-      <c r="E85" s="50"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
-      <c r="H85" s="51"/>
+      <c r="B85" s="62"/>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="64"/>
     </row>
     <row r="86" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
+      <c r="B86" s="61"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B82:H82"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A58:A65"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A72:A75"/>
     <mergeCell ref="A40:A53"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A56:A57"/>
@@ -8520,20 +8525,16 @@
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A58:A65"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B80:H80"/>
-    <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B85:H85"/>
-    <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B71:H71"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="36" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8552,20 +8553,20 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -9147,6 +9148,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="83" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="584bf6b77295f7da4f9cf4ac656056b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0744868ac059cd1623b27209cff1bde4" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -9291,17 +9303,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F706AEFA-B1CD-430D-84D8-22CA09D4DBE5}">
   <ds:schemaRefs>
@@ -9311,6 +9312,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813CB447-FC46-4A66-96F2-63C6F9CBC36C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A69048A-FE9A-4547-B799-0913FED60783}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9327,15 +9339,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813CB447-FC46-4A66-96F2-63C6F9CBC36C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
-    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF97EFE7-7996-45EC-B71C-D43E8CBB8AEA}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55253BC0-3CC7-47F8-AE7B-78EDB0012FDC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="121">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t>CUP France 26 // ANNIV</t>
+  </si>
+  <si>
+    <t>21:30/24:00</t>
   </si>
 </sst>
 </file>
@@ -4791,13 +4794,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4835,13 +4838,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4879,21 +4882,109 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4921,103 +5012,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5055,13 +5058,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5099,13 +5102,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5143,13 +5146,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5187,21 +5190,109 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5219,182 +5310,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5418,10 +5333,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5439,50 +5354,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5506,10 +5377,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5537,23 +5408,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5594,6 +5509,94 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -6595,13 +6598,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6802,6 +6805,50 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3048000" y="3629025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF356E68-6DC1-42B7-B411-DDF4487EFFA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2979964" y="14573250"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7183,7 +7230,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="44.7109375" customWidth="1"/>
@@ -8266,178 +8313,178 @@
       </c>
       <c r="H69" s="31"/>
     </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="53"/>
-      <c r="B70" s="35" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="59"/>
+      <c r="B70" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28" t="s">
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="H70" s="29"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="12" t="s">
+      <c r="H70" s="31"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="59"/>
+      <c r="B71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="31"/>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="53"/>
+      <c r="B72" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
+      <c r="H72" s="29"/>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B71" s="62"/>
-      <c r="C71" s="63"/>
-      <c r="D71" s="63"/>
-      <c r="E71" s="63"/>
-      <c r="F71" s="63"/>
-      <c r="G71" s="63"/>
-      <c r="H71" s="64"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="52" t="s">
+      <c r="B73" s="62"/>
+      <c r="C73" s="63"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="64"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B74" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C74" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="15"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="58"/>
-      <c r="B73" s="1" t="s">
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="15"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="58"/>
+      <c r="B75" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="18"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="58"/>
-      <c r="B74" s="2" t="s">
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="18"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="58"/>
+      <c r="B76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="18"/>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="53"/>
-      <c r="B75" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="17"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="B76" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="G76" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H76" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="58"/>
-      <c r="B77" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H77" s="39" t="s">
-        <v>87</v>
-      </c>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="18"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="53"/>
+      <c r="B77" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="17"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="58"/>
-      <c r="B78" s="37"/>
+      <c r="A78" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="37" t="s">
+        <v>53</v>
+      </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H78" s="39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="58"/>
+      <c r="B79" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" s="39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="58"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H78" s="19" t="s">
+      <c r="H80" s="19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="53"/>
-      <c r="B79" s="35"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16" t="s">
+    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="53"/>
+      <c r="B81" s="35"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="H79" s="17" t="s">
+      <c r="H81" s="17" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B80" s="62"/>
-      <c r="C80" s="63"/>
-      <c r="D80" s="63"/>
-      <c r="E80" s="63"/>
-      <c r="F80" s="63"/>
-      <c r="G80" s="63"/>
-      <c r="H80" s="64"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B81" s="62"/>
-      <c r="C81" s="63"/>
-      <c r="D81" s="63"/>
-      <c r="E81" s="63"/>
-      <c r="F81" s="63"/>
-      <c r="G81" s="63"/>
-      <c r="H81" s="64"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B82" s="62"/>
       <c r="C82" s="63"/>
@@ -8447,77 +8494,101 @@
       <c r="G82" s="63"/>
       <c r="H82" s="64"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="52" t="s">
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="62"/>
+      <c r="C83" s="63"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="64"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="62"/>
+      <c r="C84" s="63"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="63"/>
+      <c r="F84" s="63"/>
+      <c r="G84" s="63"/>
+      <c r="H84" s="64"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13" t="s">
+      <c r="B85" s="13"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E83" s="13" t="s">
+      <c r="E85" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F83" s="14"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="15" t="s">
+      <c r="F85" s="14"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="53"/>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16" t="s">
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="53"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E84" s="16" t="s">
+      <c r="E86" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
-      <c r="H84" s="17" t="s">
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="12" t="s">
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="62"/>
-      <c r="C85" s="63"/>
-      <c r="D85" s="63"/>
-      <c r="E85" s="63"/>
-      <c r="F85" s="63"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="64"/>
-    </row>
-    <row r="86" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
-      <c r="D86" s="61"/>
-      <c r="E86" s="61"/>
-      <c r="F86" s="61"/>
-      <c r="G86" s="61"/>
-      <c r="H86" s="61"/>
+      <c r="B87" s="62"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="64"/>
+    </row>
+    <row r="88" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="61"/>
+      <c r="C88" s="61"/>
+      <c r="D88" s="61"/>
+      <c r="E88" s="61"/>
+      <c r="F88" s="61"/>
+      <c r="G88" s="61"/>
+      <c r="H88" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B73:H73"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B80:H80"/>
-    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B88:H88"/>
     <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B85:H85"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:H83"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A85:A86"/>
     <mergeCell ref="A58:A65"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A67:A72"/>
+    <mergeCell ref="A74:A77"/>
     <mergeCell ref="A40:A53"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A56:A57"/>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55253BC0-3CC7-47F8-AE7B-78EDB0012FDC}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF97EFE7-7996-45EC-B71C-D43E8CBB8AEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="120">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -383,9 +383,6 @@
   </si>
   <si>
     <t>CUP France 26 // ANNIV</t>
-  </si>
-  <si>
-    <t>21:30/24:00</t>
   </si>
 </sst>
 </file>
@@ -4794,13 +4791,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4838,6 +4835,50 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -4849,10 +4890,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4880,23 +4965,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4924,103 +5009,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5058,13 +5055,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5102,21 +5099,241 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5144,172 +5361,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5333,10 +5418,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5354,6 +5439,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5377,10 +5506,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5408,67 +5537,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5509,94 +5594,6 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
         <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -6598,13 +6595,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6805,50 +6802,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3048000" y="3629025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF356E68-6DC1-42B7-B411-DDF4487EFFA2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2979964" y="14573250"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7230,7 +7183,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="44.7109375" customWidth="1"/>
@@ -8313,178 +8266,178 @@
       </c>
       <c r="H69" s="31"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="59"/>
-      <c r="B70" s="37" t="s">
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="53"/>
+      <c r="B70" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30" t="s">
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="59"/>
-      <c r="B71" s="2" t="s">
+      <c r="H70" s="29"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="62"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="64"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="15"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="58"/>
+      <c r="B73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="58"/>
+      <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="31"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="53"/>
-      <c r="B72" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="29"/>
-    </row>
-    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B73" s="62"/>
-      <c r="C73" s="63"/>
-      <c r="D73" s="63"/>
-      <c r="E73" s="63"/>
-      <c r="F73" s="63"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="64"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="15"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="58"/>
-      <c r="B75" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
+      <c r="C74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="18"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="53"/>
+      <c r="B75" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="17"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="58"/>
-      <c r="B76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A76" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="18"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="53"/>
-      <c r="B77" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="17"/>
+      <c r="G76" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" s="39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="58"/>
+      <c r="B77" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="H77" s="39" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="37" t="s">
-        <v>53</v>
-      </c>
+      <c r="A78" s="58"/>
+      <c r="B78" s="37"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="58"/>
-      <c r="B79" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="H79" s="39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="58"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="2" t="s">
+      <c r="F78" s="1"/>
+      <c r="G78" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="19" t="s">
+      <c r="H78" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="53"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="62"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="64"/>
+    </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="53"/>
-      <c r="B81" s="35"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>89</v>
-      </c>
+      <c r="A81" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="62"/>
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="64"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B82" s="62"/>
       <c r="C82" s="63"/>
@@ -8494,101 +8447,77 @@
       <c r="G82" s="63"/>
       <c r="H82" s="64"/>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="62"/>
-      <c r="C83" s="63"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="64"/>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" s="14"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="62"/>
-      <c r="C84" s="63"/>
-      <c r="D84" s="63"/>
-      <c r="E84" s="63"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="64"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="53"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16" t="s">
+      <c r="A84" s="53"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E86" s="16" t="s">
+      <c r="E84" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-      <c r="H86" s="17" t="s">
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="12" t="s">
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B87" s="62"/>
-      <c r="C87" s="63"/>
-      <c r="D87" s="63"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="64"/>
-    </row>
-    <row r="88" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="61"/>
-      <c r="G88" s="61"/>
-      <c r="H88" s="61"/>
+      <c r="B85" s="62"/>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="64"/>
+    </row>
+    <row r="86" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="61"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B71:H71"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B81:H81"/>
     <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B84:H84"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A83:A84"/>
     <mergeCell ref="A58:A65"/>
-    <mergeCell ref="A67:A72"/>
-    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A72:A75"/>
     <mergeCell ref="A40:A53"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A56:A57"/>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55253BC0-3CC7-47F8-AE7B-78EDB0012FDC}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF864318-39D8-43F8-B07B-728E71254EE8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="122">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -121,12 +121,6 @@
     <t>11:45/22:00</t>
   </si>
   <si>
-    <t>11:30/17:00</t>
-  </si>
-  <si>
-    <t>11:35/17:00</t>
-  </si>
-  <si>
     <t>CRUZEL Quentin</t>
   </si>
   <si>
@@ -386,6 +380,15 @@
   </si>
   <si>
     <t>21:30/24:00</t>
+  </si>
+  <si>
+    <t>11:45/17:00</t>
+  </si>
+  <si>
+    <t>11:45/17:25</t>
+  </si>
+  <si>
+    <t>17:45/24:00</t>
   </si>
 </sst>
 </file>
@@ -7262,25 +7265,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>115</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>117</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7366,7 +7369,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7384,7 +7387,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7446,7 +7449,7 @@
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
@@ -7532,10 +7535,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
@@ -7543,7 +7546,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -7564,11 +7567,11 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="18" t="s">
@@ -7577,22 +7580,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E22" s="49" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15"/>
@@ -7600,19 +7603,19 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>41</v>
-      </c>
       <c r="E23" s="43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="18"/>
@@ -7620,16 +7623,16 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="58"/>
       <c r="B24" s="25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="1"/>
@@ -7638,16 +7641,16 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="58"/>
       <c r="B25" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>44</v>
-      </c>
       <c r="E25" s="43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F25" s="23"/>
       <c r="G25" s="1"/>
@@ -7668,7 +7671,7 @@
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53"/>
       <c r="B27" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -7679,7 +7682,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -7702,13 +7705,13 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7731,13 +7734,13 @@
       <c r="E31" s="1"/>
       <c r="F31" s="30"/>
       <c r="G31" s="30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H31" s="31"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>15</v>
@@ -7760,28 +7763,28 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="58"/>
       <c r="B33" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="58"/>
       <c r="B34" s="1"/>
       <c r="C34" s="36" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -7795,19 +7798,19 @@
       <c r="A35" s="53"/>
       <c r="B35" s="16"/>
       <c r="C35" s="35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="28"/>
       <c r="G35" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -7825,7 +7828,7 @@
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
@@ -7833,7 +7836,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B38" s="62"/>
       <c r="C38" s="63"/>
@@ -7845,7 +7848,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B39" s="62"/>
       <c r="C39" s="63"/>
@@ -7857,7 +7860,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="57" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>20</v>
@@ -7877,7 +7880,7 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="58"/>
       <c r="B41" s="30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C41" s="30" t="s">
         <v>24</v>
@@ -7895,16 +7898,16 @@
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="58"/>
       <c r="B42" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -7913,16 +7916,16 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="58"/>
       <c r="B43" s="30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -7949,16 +7952,16 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="58"/>
       <c r="B45" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -7967,16 +7970,16 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="58"/>
       <c r="B46" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -7985,16 +7988,16 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="58"/>
       <c r="B47" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E47" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -8021,16 +8024,16 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="58"/>
       <c r="B49" s="30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -8039,13 +8042,13 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="58"/>
       <c r="B50" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="1"/>
@@ -8055,13 +8058,13 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="58"/>
       <c r="B51" s="30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="1"/>
@@ -8085,7 +8088,7 @@
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E53" s="28"/>
       <c r="F53" s="16"/>
@@ -8094,7 +8097,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -8116,14 +8119,14 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="52" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="14"/>
@@ -8134,10 +8137,10 @@
       <c r="A57" s="53"/>
       <c r="B57" s="16"/>
       <c r="C57" s="35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
@@ -8146,14 +8149,14 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="G58" s="38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>15</v>
@@ -8167,10 +8170,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -8182,7 +8185,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="38"/>
       <c r="H60" s="41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -8194,7 +8197,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="38"/>
       <c r="H61" s="39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -8218,7 +8221,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="38"/>
       <c r="H63" s="18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -8230,7 +8233,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="38"/>
       <c r="H64" s="41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8242,12 +8245,12 @@
       <c r="F65" s="16"/>
       <c r="G65" s="40"/>
       <c r="H65" s="42" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B66" s="65"/>
       <c r="C66" s="66"/>
@@ -8259,7 +8262,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="52" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>15</v>
@@ -8282,27 +8285,27 @@
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="58"/>
       <c r="B68" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G68" s="30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="58"/>
       <c r="B69" s="36" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -8316,14 +8319,14 @@
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="30"/>
       <c r="G70" s="30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H70" s="31"/>
     </row>
@@ -8342,7 +8345,7 @@
     <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="53"/>
       <c r="B72" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
@@ -8353,7 +8356,7 @@
     </row>
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B73" s="62"/>
       <c r="C73" s="63"/>
@@ -8365,7 +8368,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="52" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>20</v>
@@ -8382,7 +8385,7 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="58"/>
       <c r="B75" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>24</v>
@@ -8410,7 +8413,7 @@
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="53"/>
       <c r="B77" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="16" t="s">
         <v>26</v>
@@ -8423,35 +8426,35 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="57" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B78" s="37" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="G78" s="38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="58"/>
       <c r="B79" s="37" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -8476,15 +8479,15 @@
       <c r="E81" s="16"/>
       <c r="F81" s="16"/>
       <c r="G81" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B82" s="62"/>
       <c r="C82" s="63"/>
@@ -8496,7 +8499,7 @@
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B83" s="62"/>
       <c r="C83" s="63"/>
@@ -8508,7 +8511,7 @@
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B84" s="62"/>
       <c r="C84" s="63"/>
@@ -8520,7 +8523,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B85" s="13"/>
       <c r="C85" s="13"/>
@@ -8541,20 +8544,20 @@
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
       <c r="H86" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B87" s="62"/>
       <c r="C87" s="63"/>
@@ -8625,7 +8628,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" s="68"/>
       <c r="D4" s="68"/>
@@ -8633,7 +8636,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="69" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" s="69"/>
@@ -8644,16 +8647,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8760,7 +8763,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -8777,7 +8780,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -8794,7 +8797,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -8811,7 +8814,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8828,7 +8831,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8845,7 +8848,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8862,7 +8865,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8879,7 +8882,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8896,7 +8899,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8913,7 +8916,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8930,7 +8933,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8947,7 +8950,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8964,7 +8967,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8981,7 +8984,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8998,7 +9001,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -9015,7 +9018,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -9032,7 +9035,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -9049,7 +9052,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9066,7 +9069,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9083,7 +9086,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9100,7 +9103,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9117,7 +9120,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9167,40 +9170,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF864318-39D8-43F8-B07B-728E71254EE8}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF97EFE7-7996-45EC-B71C-D43E8CBB8AEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="120">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -121,6 +121,12 @@
     <t>11:45/22:00</t>
   </si>
   <si>
+    <t>11:30/17:00</t>
+  </si>
+  <si>
+    <t>11:35/17:00</t>
+  </si>
+  <si>
     <t>CRUZEL Quentin</t>
   </si>
   <si>
@@ -377,18 +383,6 @@
   </si>
   <si>
     <t>CUP France 26 // ANNIV</t>
-  </si>
-  <si>
-    <t>21:30/24:00</t>
-  </si>
-  <si>
-    <t>11:45/17:00</t>
-  </si>
-  <si>
-    <t>11:45/17:25</t>
-  </si>
-  <si>
-    <t>17:45/24:00</t>
   </si>
 </sst>
 </file>
@@ -4797,13 +4791,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4841,6 +4835,50 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -4852,10 +4890,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4883,23 +4965,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4927,103 +5009,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5061,13 +5055,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5105,21 +5099,241 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5147,172 +5361,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5336,10 +5418,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5357,6 +5439,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5380,10 +5506,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5411,67 +5537,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5512,94 +5594,6 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
         <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -6601,13 +6595,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6808,50 +6802,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3048000" y="3629025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF356E68-6DC1-42B7-B411-DDF4487EFFA2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2979964" y="14573250"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7233,7 +7183,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="44.7109375" customWidth="1"/>
@@ -7265,25 +7215,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7369,7 +7319,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7387,7 +7337,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7449,7 +7399,7 @@
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
@@ -7535,10 +7485,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
@@ -7546,7 +7496,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -7567,11 +7517,11 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="18" t="s">
@@ -7580,22 +7530,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E22" s="49" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15"/>
@@ -7603,19 +7553,19 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="18"/>
@@ -7623,16 +7573,16 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="58"/>
       <c r="B24" s="25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="1"/>
@@ -7641,16 +7591,16 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="58"/>
       <c r="B25" s="23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F25" s="23"/>
       <c r="G25" s="1"/>
@@ -7671,7 +7621,7 @@
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53"/>
       <c r="B27" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -7682,7 +7632,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -7705,13 +7655,13 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7734,13 +7684,13 @@
       <c r="E31" s="1"/>
       <c r="F31" s="30"/>
       <c r="G31" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H31" s="31"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>15</v>
@@ -7763,28 +7713,28 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="58"/>
       <c r="B33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="58"/>
       <c r="B34" s="1"/>
       <c r="C34" s="36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -7798,19 +7748,19 @@
       <c r="A35" s="53"/>
       <c r="B35" s="16"/>
       <c r="C35" s="35" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="28"/>
       <c r="G35" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -7828,7 +7778,7 @@
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
@@ -7836,7 +7786,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B38" s="62"/>
       <c r="C38" s="63"/>
@@ -7848,7 +7798,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B39" s="62"/>
       <c r="C39" s="63"/>
@@ -7860,7 +7810,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="57" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>20</v>
@@ -7880,7 +7830,7 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="58"/>
       <c r="B41" s="30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C41" s="30" t="s">
         <v>24</v>
@@ -7898,16 +7848,16 @@
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="58"/>
       <c r="B42" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -7916,16 +7866,16 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="58"/>
       <c r="B43" s="30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -7952,16 +7902,16 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="58"/>
       <c r="B45" s="30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -7970,16 +7920,16 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="58"/>
       <c r="B46" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -7988,16 +7938,16 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="58"/>
       <c r="B47" s="30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E47" s="30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -8024,16 +7974,16 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="58"/>
       <c r="B49" s="30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -8042,13 +7992,13 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="58"/>
       <c r="B50" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="1"/>
@@ -8058,13 +8008,13 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="58"/>
       <c r="B51" s="30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="1"/>
@@ -8088,7 +8038,7 @@
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E53" s="28"/>
       <c r="F53" s="16"/>
@@ -8097,7 +8047,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="52" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -8119,14 +8069,14 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="52" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="14"/>
@@ -8137,10 +8087,10 @@
       <c r="A57" s="53"/>
       <c r="B57" s="16"/>
       <c r="C57" s="35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
@@ -8149,14 +8099,14 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="G58" s="38" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>15</v>
@@ -8170,10 +8120,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -8185,7 +8135,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="38"/>
       <c r="H60" s="41" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -8197,7 +8147,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="38"/>
       <c r="H61" s="39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -8221,7 +8171,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="38"/>
       <c r="H63" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -8233,7 +8183,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="38"/>
       <c r="H64" s="41" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8245,12 +8195,12 @@
       <c r="F65" s="16"/>
       <c r="G65" s="40"/>
       <c r="H65" s="42" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B66" s="65"/>
       <c r="C66" s="66"/>
@@ -8262,7 +8212,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="52" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>15</v>
@@ -8285,27 +8235,27 @@
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="58"/>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G68" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="58"/>
       <c r="B69" s="36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -8316,178 +8266,178 @@
       </c>
       <c r="H69" s="31"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="59"/>
-      <c r="B70" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="59"/>
-      <c r="B71" s="2" t="s">
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="53"/>
+      <c r="B70" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="H70" s="29"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="62"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="64"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="15"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="58"/>
+      <c r="B73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="58"/>
+      <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="31"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="53"/>
-      <c r="B72" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="29"/>
-    </row>
-    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="62"/>
-      <c r="C73" s="63"/>
-      <c r="D73" s="63"/>
-      <c r="E73" s="63"/>
-      <c r="F73" s="63"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="64"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="15"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="58"/>
-      <c r="B75" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
+      <c r="C74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="18"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="53"/>
+      <c r="B75" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="17"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="58"/>
-      <c r="B76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A76" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="18"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="53"/>
-      <c r="B77" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="17"/>
+      <c r="G76" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" s="39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="58"/>
+      <c r="B77" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="H77" s="39" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="37" t="s">
-        <v>51</v>
-      </c>
+      <c r="A78" s="58"/>
+      <c r="B78" s="37"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="58"/>
-      <c r="B79" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="H79" s="39" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="58"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="2" t="s">
+      <c r="F78" s="1"/>
+      <c r="G78" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="19" t="s">
+      <c r="H78" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="53"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="62"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="64"/>
+    </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="53"/>
-      <c r="B81" s="35"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="A81" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="62"/>
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="64"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B82" s="62"/>
       <c r="C82" s="63"/>
@@ -8497,101 +8447,77 @@
       <c r="G82" s="63"/>
       <c r="H82" s="64"/>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B83" s="62"/>
-      <c r="C83" s="63"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="64"/>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" s="14"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B84" s="62"/>
-      <c r="C84" s="63"/>
-      <c r="D84" s="63"/>
-      <c r="E84" s="63"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="64"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="53"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-      <c r="H86" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" s="62"/>
-      <c r="C87" s="63"/>
-      <c r="D87" s="63"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="64"/>
-    </row>
-    <row r="88" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="61"/>
-      <c r="G88" s="61"/>
-      <c r="H88" s="61"/>
+      <c r="A84" s="53"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" s="62"/>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="64"/>
+    </row>
+    <row r="86" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="61"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B71:H71"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B81:H81"/>
     <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B84:H84"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A83:A84"/>
     <mergeCell ref="A58:A65"/>
-    <mergeCell ref="A67:A72"/>
-    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A72:A75"/>
     <mergeCell ref="A40:A53"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A56:A57"/>
@@ -8628,7 +8554,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="68" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C4" s="68"/>
       <c r="D4" s="68"/>
@@ -8636,7 +8562,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="69" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" s="69"/>
@@ -8647,16 +8573,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8763,7 +8689,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -8780,7 +8706,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -8797,7 +8723,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -8814,7 +8740,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8831,7 +8757,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8848,7 +8774,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8865,7 +8791,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8882,7 +8808,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8899,7 +8825,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8916,7 +8842,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8933,7 +8859,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8950,7 +8876,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8967,7 +8893,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8984,7 +8910,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -9001,7 +8927,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -9018,7 +8944,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -9035,7 +8961,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -9052,7 +8978,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9069,7 +8995,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9086,7 +9012,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9103,7 +9029,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9120,7 +9046,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9170,40 +9096,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF864318-39D8-43F8-B07B-728E71254EE8}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67428BA2-5A2B-4348-BCB9-F88F9AED346F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,9 +124,6 @@
     <t>CRUZEL Quentin</t>
   </si>
   <si>
-    <t>16:30/24:00</t>
-  </si>
-  <si>
     <t>DE NOUEL Maxime</t>
   </si>
   <si>
@@ -389,6 +386,9 @@
   </si>
   <si>
     <t>17:45/24:00</t>
+  </si>
+  <si>
+    <t>16:00/24:00</t>
   </si>
 </sst>
 </file>
@@ -7265,25 +7265,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>114</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>115</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>117</v>
-      </c>
       <c r="H3" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7369,7 +7369,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7387,7 +7387,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
@@ -7535,10 +7535,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>119</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>120</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
@@ -7567,11 +7567,11 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="20" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="18" t="s">
@@ -7580,22 +7580,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="50" t="s">
-        <v>36</v>
-      </c>
       <c r="E22" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="50" t="s">
         <v>35</v>
-      </c>
-      <c r="F22" s="50" t="s">
-        <v>36</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15"/>
@@ -7603,19 +7603,19 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="D23" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="23" t="s">
-        <v>39</v>
-      </c>
       <c r="E23" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="23" t="s">
         <v>38</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>39</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="18"/>
@@ -7623,16 +7623,16 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="58"/>
       <c r="B24" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="1"/>
@@ -7641,16 +7641,16 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="58"/>
       <c r="B25" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="D25" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="43" t="s">
-        <v>42</v>
-      </c>
       <c r="E25" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" s="23"/>
       <c r="G25" s="1"/>
@@ -7671,7 +7671,7 @@
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53"/>
       <c r="B27" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -7705,13 +7705,13 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H29" s="31" t="s">
         <v>45</v>
-      </c>
-      <c r="G29" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="H29" s="31" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7734,13 +7734,13 @@
       <c r="E31" s="1"/>
       <c r="F31" s="30"/>
       <c r="G31" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H31" s="31"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>15</v>
@@ -7763,28 +7763,28 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="58"/>
       <c r="B33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="31" t="s">
         <v>45</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="H33" s="31" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="58"/>
       <c r="B34" s="1"/>
       <c r="C34" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -7798,19 +7798,19 @@
       <c r="A35" s="53"/>
       <c r="B35" s="16"/>
       <c r="C35" s="35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="28"/>
       <c r="G35" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -7828,7 +7828,7 @@
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" s="62"/>
       <c r="C38" s="63"/>
@@ -7848,7 +7848,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" s="62"/>
       <c r="C39" s="63"/>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>20</v>
@@ -7880,7 +7880,7 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="58"/>
       <c r="B41" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="30" t="s">
         <v>24</v>
@@ -7898,16 +7898,16 @@
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="58"/>
       <c r="B42" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -7916,16 +7916,16 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="58"/>
       <c r="B43" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -7952,16 +7952,16 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="58"/>
       <c r="B45" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -7970,16 +7970,16 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="58"/>
       <c r="B46" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -7988,16 +7988,16 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="58"/>
       <c r="B47" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E47" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -8024,16 +8024,16 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="58"/>
       <c r="B49" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -8042,13 +8042,13 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="58"/>
       <c r="B50" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="1"/>
@@ -8058,13 +8058,13 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="58"/>
       <c r="B51" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="1"/>
@@ -8088,7 +8088,7 @@
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E53" s="28"/>
       <c r="F53" s="16"/>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -8119,14 +8119,14 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="14"/>
@@ -8137,10 +8137,10 @@
       <c r="A57" s="53"/>
       <c r="B57" s="16"/>
       <c r="C57" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="35" t="s">
         <v>68</v>
-      </c>
-      <c r="D57" s="35" t="s">
-        <v>69</v>
       </c>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
@@ -8149,14 +8149,14 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="G58" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>15</v>
@@ -8170,10 +8170,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="H59" s="18" t="s">
         <v>72</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -8185,7 +8185,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="38"/>
       <c r="H60" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -8197,7 +8197,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="38"/>
       <c r="H61" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -8221,7 +8221,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="38"/>
       <c r="H63" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="38"/>
       <c r="H64" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8245,12 +8245,12 @@
       <c r="F65" s="16"/>
       <c r="G65" s="40"/>
       <c r="H65" s="42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B66" s="65"/>
       <c r="C66" s="66"/>
@@ -8262,7 +8262,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>15</v>
@@ -8285,27 +8285,27 @@
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="58"/>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H68" s="31" t="s">
         <v>45</v>
-      </c>
-      <c r="G68" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="H68" s="31" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="58"/>
       <c r="B69" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -8319,14 +8319,14 @@
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="30"/>
       <c r="G70" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H70" s="31"/>
     </row>
@@ -8345,7 +8345,7 @@
     <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="53"/>
       <c r="B72" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
@@ -8356,7 +8356,7 @@
     </row>
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B73" s="62"/>
       <c r="C73" s="63"/>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>20</v>
@@ -8385,7 +8385,7 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="58"/>
       <c r="B75" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>24</v>
@@ -8413,7 +8413,7 @@
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="53"/>
       <c r="B77" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" s="16" t="s">
         <v>26</v>
@@ -8426,35 +8426,35 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="G78" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="58"/>
       <c r="B79" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -8479,15 +8479,15 @@
       <c r="E81" s="16"/>
       <c r="F81" s="16"/>
       <c r="G81" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H81" s="17" t="s">
         <v>86</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" s="62"/>
       <c r="C82" s="63"/>
@@ -8499,7 +8499,7 @@
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B83" s="62"/>
       <c r="C83" s="63"/>
@@ -8511,7 +8511,7 @@
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B84" s="62"/>
       <c r="C84" s="63"/>
@@ -8523,7 +8523,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B85" s="13"/>
       <c r="C85" s="13"/>
@@ -8544,20 +8544,20 @@
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
       <c r="H86" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B87" s="62"/>
       <c r="C87" s="63"/>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="68"/>
       <c r="D4" s="68"/>
@@ -8636,7 +8636,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" s="69"/>
@@ -8647,16 +8647,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8780,7 +8780,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -8797,7 +8797,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -8814,7 +8814,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8831,7 +8831,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8848,7 +8848,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8865,7 +8865,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8899,7 +8899,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8916,7 +8916,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8933,7 +8933,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8950,7 +8950,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -9001,7 +9001,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -9018,7 +9018,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -9035,7 +9035,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -9052,7 +9052,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9069,7 +9069,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9086,7 +9086,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9103,7 +9103,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9120,7 +9120,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9170,40 +9170,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>104</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67428BA2-5A2B-4348-BCB9-F88F9AED346F}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0596284D-392B-425B-9D8C-C4B76A4CD3CB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="121">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -236,9 +236,6 @@
   </si>
   <si>
     <t>ANNIV</t>
-  </si>
-  <si>
-    <t>14:00/18:00</t>
   </si>
   <si>
     <t>09:30/10:15</t>
@@ -821,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -938,9 +935,6 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4257,50 +4251,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7240,50 +7190,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51" t="s">
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>113</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>114</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>116</v>
-      </c>
       <c r="H3" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7316,18 +7266,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="56"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="55"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="51" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7343,7 +7293,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7357,7 +7307,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="56" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7368,8 +7318,8 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="47" t="s">
-        <v>109</v>
+      <c r="F8" s="46" t="s">
+        <v>108</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7377,7 +7327,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="58"/>
+      <c r="A9" s="57"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7386,8 +7336,8 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="48" t="s">
-        <v>110</v>
+      <c r="F9" s="47" t="s">
+        <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7395,7 +7345,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="58"/>
+      <c r="A10" s="57"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7404,14 +7354,14 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="58"/>
+      <c r="A11" s="57"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7427,21 +7377,21 @@
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="58"/>
+      <c r="A12" s="57"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="45" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="53"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
@@ -7449,13 +7399,13 @@
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="51" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7469,7 +7419,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7481,7 +7431,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="51" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7495,7 +7445,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="53"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7507,7 +7457,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="51" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7527,7 +7477,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7535,17 +7485,17 @@
         <v>31</v>
       </c>
       <c r="D19" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>118</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>119</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="51" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="13"/>
@@ -7563,7 +7513,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="59"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
@@ -7571,7 +7521,7 @@
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="18" t="s">
@@ -7579,39 +7529,39 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="51" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D22" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="49" t="s">
+      <c r="E22" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="49" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="58"/>
+      <c r="A23" s="57"/>
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="42" t="s">
         <v>37</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="42" t="s">
         <v>37</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -7621,17 +7571,17 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="58"/>
+      <c r="A24" s="57"/>
       <c r="B24" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="43" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="23"/>
@@ -7639,17 +7589,17 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
+      <c r="A25" s="57"/>
       <c r="B25" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="42" t="s">
         <v>40</v>
       </c>
       <c r="F25" s="23"/>
@@ -7657,31 +7607,31 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="58"/>
+      <c r="A26" s="57"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="53"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="52" t="s">
+      <c r="A28" s="51" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="13"/>
@@ -7699,7 +7649,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="60"/>
+      <c r="A29" s="59"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -7708,14 +7658,14 @@
         <v>44</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H29" s="31" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="60"/>
+      <c r="A30" s="59"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -7727,19 +7677,19 @@
       <c r="H30" s="31"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="59"/>
+      <c r="A31" s="58"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="30"/>
       <c r="G31" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H31" s="31"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="51" t="s">
         <v>46</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -7761,7 +7711,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="58"/>
+      <c r="A33" s="57"/>
       <c r="B33" s="1" t="s">
         <v>47</v>
       </c>
@@ -7774,14 +7724,14 @@
         <v>44</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H33" s="31" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="58"/>
+      <c r="A34" s="57"/>
       <c r="B34" s="1"/>
       <c r="C34" s="36" t="s">
         <v>50</v>
@@ -7795,7 +7745,7 @@
       <c r="H34" s="31"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="53"/>
+      <c r="A35" s="52"/>
       <c r="B35" s="16"/>
       <c r="C35" s="35" t="s">
         <v>51</v>
@@ -7804,12 +7754,12 @@
       <c r="E35" s="16"/>
       <c r="F35" s="28"/>
       <c r="G35" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="52" t="s">
+      <c r="A36" s="51" t="s">
         <v>52</v>
       </c>
       <c r="B36" s="13"/>
@@ -7823,12 +7773,12 @@
       <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="53"/>
+      <c r="A37" s="52"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
@@ -7838,28 +7788,28 @@
       <c r="A38" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="62"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="64"/>
+      <c r="B38" s="61"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="63"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="62"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="64"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="63"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="56" t="s">
         <v>56</v>
       </c>
       <c r="B40" s="30" t="s">
@@ -7878,7 +7828,7 @@
       <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="58"/>
+      <c r="A41" s="57"/>
       <c r="B41" s="30" t="s">
         <v>57</v>
       </c>
@@ -7896,7 +7846,7 @@
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="58"/>
+      <c r="A42" s="57"/>
       <c r="B42" s="33" t="s">
         <v>58</v>
       </c>
@@ -7914,7 +7864,7 @@
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="58"/>
+      <c r="A43" s="57"/>
       <c r="B43" s="30" t="s">
         <v>59</v>
       </c>
@@ -7932,7 +7882,7 @@
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="58"/>
+      <c r="A44" s="57"/>
       <c r="B44" s="33" t="s">
         <v>20</v>
       </c>
@@ -7950,7 +7900,7 @@
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="58"/>
+      <c r="A45" s="57"/>
       <c r="B45" s="30" t="s">
         <v>60</v>
       </c>
@@ -7968,7 +7918,7 @@
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="58"/>
+      <c r="A46" s="57"/>
       <c r="B46" s="33" t="s">
         <v>58</v>
       </c>
@@ -7986,7 +7936,7 @@
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="58"/>
+      <c r="A47" s="57"/>
       <c r="B47" s="30" t="s">
         <v>61</v>
       </c>
@@ -8004,7 +7954,7 @@
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="58"/>
+      <c r="A48" s="57"/>
       <c r="B48" s="33" t="s">
         <v>20</v>
       </c>
@@ -8022,7 +7972,7 @@
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="58"/>
+      <c r="A49" s="57"/>
       <c r="B49" s="30" t="s">
         <v>62</v>
       </c>
@@ -8040,7 +7990,7 @@
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="58"/>
+      <c r="A50" s="57"/>
       <c r="B50" s="33" t="s">
         <v>58</v>
       </c>
@@ -8056,7 +8006,7 @@
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="58"/>
+      <c r="A51" s="57"/>
       <c r="B51" s="30" t="s">
         <v>63</v>
       </c>
@@ -8072,7 +8022,7 @@
       <c r="H51" s="18"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="58"/>
+      <c r="A52" s="57"/>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="33" t="s">
@@ -8084,7 +8034,7 @@
       <c r="H52" s="18"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="53"/>
+      <c r="A53" s="52"/>
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28" t="s">
@@ -8096,7 +8046,7 @@
       <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="52" t="s">
+      <c r="A54" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="13"/>
@@ -8108,7 +8058,7 @@
       <c r="H54" s="15"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="53"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -8118,7 +8068,7 @@
       <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="52" t="s">
+      <c r="A56" s="51" t="s">
         <v>66</v>
       </c>
       <c r="B56" s="13"/>
@@ -8134,7 +8084,7 @@
       <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="53"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="16"/>
       <c r="C57" s="35" t="s">
         <v>67</v>
@@ -8148,121 +8098,117 @@
       <c r="H57" s="17"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="57" t="s">
+      <c r="A58" s="56" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="G58" s="38" t="s">
-        <v>70</v>
-      </c>
+      <c r="G58" s="1"/>
       <c r="H58" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="58"/>
+      <c r="A59" s="57"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="38" t="s">
+      <c r="G59" s="1"/>
+      <c r="H59" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H59" s="18" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="58"/>
+      <c r="A60" s="57"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="41" t="s">
+      <c r="G60" s="1"/>
+      <c r="H60" s="40" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="58"/>
+      <c r="A61" s="57"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="38"/>
+      <c r="G61" s="1"/>
       <c r="H61" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="58"/>
+      <c r="A62" s="57"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="38"/>
+      <c r="G62" s="1"/>
       <c r="H62" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="58"/>
+      <c r="A63" s="57"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="38"/>
+      <c r="G63" s="1"/>
       <c r="H63" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="58"/>
+      <c r="A64" s="57"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="41" t="s">
+      <c r="G64" s="1"/>
+      <c r="H64" s="40" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="53"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="42" t="s">
-        <v>75</v>
+      <c r="G65" s="16"/>
+      <c r="H65" s="41" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="64"/>
+      <c r="C66" s="65"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="65"/>
+      <c r="H66" s="66"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="51" t="s">
         <v>76</v>
-      </c>
-      <c r="B66" s="65"/>
-      <c r="C66" s="66"/>
-      <c r="D66" s="66"/>
-      <c r="E66" s="66"/>
-      <c r="F66" s="66"/>
-      <c r="G66" s="66"/>
-      <c r="H66" s="67"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="52" t="s">
-        <v>77</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>15</v>
@@ -8283,9 +8229,9 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="58"/>
+      <c r="A68" s="57"/>
       <c r="B68" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>47</v>
@@ -8296,14 +8242,14 @@
         <v>44</v>
       </c>
       <c r="G68" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H68" s="31" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="58"/>
+      <c r="A69" s="57"/>
       <c r="B69" s="36" t="s">
         <v>50</v>
       </c>
@@ -8317,7 +8263,7 @@
       <c r="H69" s="31"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="59"/>
+      <c r="A70" s="58"/>
       <c r="B70" s="37" t="s">
         <v>68</v>
       </c>
@@ -8326,12 +8272,12 @@
       <c r="E70" s="1"/>
       <c r="F70" s="30"/>
       <c r="G70" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H70" s="31"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="59"/>
+      <c r="A71" s="58"/>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
@@ -8343,9 +8289,9 @@
       <c r="H71" s="31"/>
     </row>
     <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="53"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
@@ -8356,19 +8302,19 @@
     </row>
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="61"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="62"/>
+      <c r="E73" s="62"/>
+      <c r="F73" s="62"/>
+      <c r="G73" s="62"/>
+      <c r="H73" s="63"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="51" t="s">
         <v>79</v>
-      </c>
-      <c r="B73" s="62"/>
-      <c r="C73" s="63"/>
-      <c r="D73" s="63"/>
-      <c r="E73" s="63"/>
-      <c r="F73" s="63"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="64"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="52" t="s">
-        <v>80</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>20</v>
@@ -8383,9 +8329,9 @@
       <c r="H74" s="15"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="58"/>
+      <c r="A75" s="57"/>
       <c r="B75" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>24</v>
@@ -8397,7 +8343,7 @@
       <c r="H75" s="18"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="58"/>
+      <c r="A76" s="57"/>
       <c r="B76" s="2" t="s">
         <v>15</v>
       </c>
@@ -8411,9 +8357,9 @@
       <c r="H76" s="18"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="53"/>
+      <c r="A77" s="52"/>
       <c r="B77" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="16" t="s">
         <v>26</v>
@@ -8425,8 +8371,8 @@
       <c r="H77" s="17"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="57" t="s">
-        <v>83</v>
+      <c r="A78" s="56" t="s">
+        <v>82</v>
       </c>
       <c r="B78" s="37" t="s">
         <v>50</v>
@@ -8442,7 +8388,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="58"/>
+      <c r="A79" s="57"/>
       <c r="B79" s="37" t="s">
         <v>51</v>
       </c>
@@ -8451,14 +8397,14 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="58"/>
+      <c r="A80" s="57"/>
       <c r="B80" s="37"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -8472,58 +8418,58 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="53"/>
+      <c r="A81" s="52"/>
       <c r="B81" s="35"/>
       <c r="C81" s="16"/>
       <c r="D81" s="16"/>
       <c r="E81" s="16"/>
       <c r="F81" s="16"/>
       <c r="G81" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H81" s="17" t="s">
         <v>85</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B82" s="62"/>
-      <c r="C82" s="63"/>
-      <c r="D82" s="63"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="63"/>
-      <c r="G82" s="63"/>
-      <c r="H82" s="64"/>
+        <v>86</v>
+      </c>
+      <c r="B82" s="61"/>
+      <c r="C82" s="62"/>
+      <c r="D82" s="62"/>
+      <c r="E82" s="62"/>
+      <c r="F82" s="62"/>
+      <c r="G82" s="62"/>
+      <c r="H82" s="63"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="62"/>
-      <c r="C83" s="63"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="64"/>
+        <v>87</v>
+      </c>
+      <c r="B83" s="61"/>
+      <c r="C83" s="62"/>
+      <c r="D83" s="62"/>
+      <c r="E83" s="62"/>
+      <c r="F83" s="62"/>
+      <c r="G83" s="62"/>
+      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="61"/>
+      <c r="C84" s="62"/>
+      <c r="D84" s="62"/>
+      <c r="E84" s="62"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="63"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="51" t="s">
         <v>89</v>
-      </c>
-      <c r="B84" s="62"/>
-      <c r="C84" s="63"/>
-      <c r="D84" s="63"/>
-      <c r="E84" s="63"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="64"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="52" t="s">
-        <v>90</v>
       </c>
       <c r="B85" s="13"/>
       <c r="C85" s="13"/>
@@ -8540,7 +8486,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="53"/>
+      <c r="A86" s="52"/>
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16" t="s">
@@ -8552,29 +8498,29 @@
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
       <c r="H86" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B87" s="62"/>
-      <c r="C87" s="63"/>
-      <c r="D87" s="63"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="64"/>
+        <v>91</v>
+      </c>
+      <c r="B87" s="61"/>
+      <c r="C87" s="62"/>
+      <c r="D87" s="62"/>
+      <c r="E87" s="62"/>
+      <c r="F87" s="62"/>
+      <c r="G87" s="62"/>
+      <c r="H87" s="63"/>
     </row>
     <row r="88" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="61"/>
-      <c r="G88" s="61"/>
-      <c r="H88" s="61"/>
+      <c r="B88" s="60"/>
+      <c r="C88" s="60"/>
+      <c r="D88" s="60"/>
+      <c r="E88" s="60"/>
+      <c r="F88" s="60"/>
+      <c r="G88" s="60"/>
+      <c r="H88" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -8627,36 +8573,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8967,7 +8913,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8984,7 +8930,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -9001,7 +8947,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -9018,7 +8964,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -9035,7 +8981,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -9052,7 +8998,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9069,7 +9015,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9086,7 +9032,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9103,7 +9049,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9120,7 +9066,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9170,40 +9116,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0596284D-392B-425B-9D8C-C4B76A4CD3CB}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF97EFE7-7996-45EC-B71C-D43E8CBB8AEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="120">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -121,9 +121,18 @@
     <t>11:45/22:00</t>
   </si>
   <si>
+    <t>11:30/17:00</t>
+  </si>
+  <si>
+    <t>11:35/17:00</t>
+  </si>
+  <si>
     <t>CRUZEL Quentin</t>
   </si>
   <si>
+    <t>16:30/24:00</t>
+  </si>
+  <si>
     <t>DE NOUEL Maxime</t>
   </si>
   <si>
@@ -238,6 +247,9 @@
     <t>ANNIV</t>
   </si>
   <si>
+    <t>14:00/18:00</t>
+  </si>
+  <si>
     <t>09:30/10:15</t>
   </si>
   <si>
@@ -371,21 +383,6 @@
   </si>
   <si>
     <t>CUP France 26 // ANNIV</t>
-  </si>
-  <si>
-    <t>21:30/24:00</t>
-  </si>
-  <si>
-    <t>11:45/17:00</t>
-  </si>
-  <si>
-    <t>11:45/17:25</t>
-  </si>
-  <si>
-    <t>17:45/24:00</t>
-  </si>
-  <si>
-    <t>16:00/24:00</t>
   </si>
 </sst>
 </file>
@@ -818,7 +815,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -935,6 +932,9 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4261,6 +4261,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>57</xdr:row>
@@ -4747,13 +4791,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4791,6 +4835,50 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -4802,10 +4890,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4833,23 +4965,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4877,103 +5009,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5011,13 +5055,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5055,21 +5099,241 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5097,172 +5361,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5286,10 +5418,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5307,6 +5439,50 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5330,10 +5506,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5361,67 +5537,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5462,94 +5594,6 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
         <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -6551,13 +6595,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6758,50 +6802,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3048000" y="3629025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF356E68-6DC1-42B7-B411-DDF4487EFFA2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2979964" y="14573250"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7183,57 +7183,57 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7266,18 +7266,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="52" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7293,7 +7293,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="52"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7307,7 +7307,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="57" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7318,8 +7318,8 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="46" t="s">
-        <v>108</v>
+      <c r="F8" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -7327,7 +7327,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7336,8 +7336,8 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="47" t="s">
-        <v>109</v>
+      <c r="F9" s="48" t="s">
+        <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -7345,7 +7345,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="57"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7354,14 +7354,14 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="46" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="57"/>
+      <c r="A11" s="58"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7377,21 +7377,21 @@
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="57"/>
+      <c r="A12" s="58"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="46" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="52"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
@@ -7399,13 +7399,13 @@
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="52" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7419,7 +7419,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="52"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7431,7 +7431,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="52" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7445,7 +7445,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="52"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7457,7 +7457,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="52" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7477,7 +7477,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="52"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7485,18 +7485,18 @@
         <v>31</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
-        <v>32</v>
+      <c r="A20" s="52" t="s">
+        <v>34</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -7513,15 +7513,15 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="20" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="18" t="s">
@@ -7529,110 +7529,110 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="s">
-        <v>33</v>
+      <c r="A22" s="52" t="s">
+        <v>36</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="49" t="s">
-        <v>35</v>
+      <c r="C22" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>38</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="57"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>40</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>40</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="57"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>37</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="1"/>
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="57"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>43</v>
       </c>
       <c r="F25" s="23"/>
       <c r="G25" s="1"/>
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="57"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="52"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
+        <v>45</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
-        <v>43</v>
+      <c r="A28" s="52" t="s">
+        <v>46</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -7649,23 +7649,23 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="59"/>
+      <c r="A29" s="60"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="32" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
+      <c r="A30" s="60"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -7677,20 +7677,20 @@
       <c r="H30" s="31"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="58"/>
+      <c r="A31" s="59"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="30"/>
       <c r="G31" s="30" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H31" s="31"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="51" t="s">
-        <v>46</v>
+      <c r="A32" s="52" t="s">
+        <v>49</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>15</v>
@@ -7711,30 +7711,30 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="57"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="32" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="57"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="1"/>
       <c r="C34" s="36" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -7745,22 +7745,22 @@
       <c r="H34" s="31"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="52"/>
+      <c r="A35" s="53"/>
       <c r="B35" s="16"/>
       <c r="C35" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="28"/>
       <c r="G35" s="28" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="51" t="s">
-        <v>52</v>
+      <c r="A36" s="52" t="s">
+        <v>55</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -7773,12 +7773,12 @@
       <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="52"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
@@ -7786,31 +7786,31 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="63"/>
+        <v>57</v>
+      </c>
+      <c r="B38" s="62"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="64"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="61"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="63"/>
+        <v>58</v>
+      </c>
+      <c r="B39" s="62"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="64"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="56" t="s">
-        <v>56</v>
+      <c r="A40" s="57" t="s">
+        <v>59</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>20</v>
@@ -7828,9 +7828,9 @@
       <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="57"/>
+      <c r="A41" s="58"/>
       <c r="B41" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C41" s="30" t="s">
         <v>24</v>
@@ -7846,43 +7846,43 @@
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="57"/>
+      <c r="A42" s="58"/>
       <c r="B42" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="57"/>
+      <c r="A43" s="58"/>
       <c r="B43" s="30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="57"/>
+      <c r="A44" s="58"/>
       <c r="B44" s="33" t="s">
         <v>20</v>
       </c>
@@ -7900,61 +7900,61 @@
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="57"/>
+      <c r="A45" s="58"/>
       <c r="B45" s="30" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="57"/>
+      <c r="A46" s="58"/>
       <c r="B46" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="57"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E47" s="30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="57"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="33" t="s">
         <v>20</v>
       </c>
@@ -7972,33 +7972,33 @@
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="57"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="57"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="1"/>
@@ -8006,15 +8006,15 @@
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="57"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="1"/>
@@ -8022,7 +8022,7 @@
       <c r="H51" s="18"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="57"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="33" t="s">
@@ -8034,11 +8034,11 @@
       <c r="H52" s="18"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="52"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E53" s="28"/>
       <c r="F53" s="16"/>
@@ -8046,8 +8046,8 @@
       <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="51" t="s">
-        <v>65</v>
+      <c r="A54" s="52" t="s">
+        <v>68</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -8058,7 +8058,7 @@
       <c r="H54" s="15"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="52"/>
+      <c r="A55" s="53"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -8068,15 +8068,15 @@
       <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="51" t="s">
-        <v>66</v>
+      <c r="A56" s="52" t="s">
+        <v>69</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="34" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="14"/>
@@ -8084,13 +8084,13 @@
       <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="52"/>
+      <c r="A57" s="53"/>
       <c r="B57" s="16"/>
       <c r="C57" s="35" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
@@ -8098,117 +8098,121 @@
       <c r="H57" s="17"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="56" t="s">
-        <v>69</v>
+      <c r="A58" s="57" t="s">
+        <v>72</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="G58" s="1"/>
+      <c r="G58" s="38" t="s">
+        <v>73</v>
+      </c>
       <c r="H58" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="57"/>
+      <c r="A59" s="58"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
+      <c r="G59" s="38" t="s">
+        <v>74</v>
+      </c>
       <c r="H59" s="18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="57"/>
+      <c r="A60" s="58"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="40" t="s">
-        <v>70</v>
+      <c r="G60" s="38"/>
+      <c r="H60" s="41" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="57"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
+      <c r="G61" s="38"/>
       <c r="H61" s="39" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="57"/>
+      <c r="A62" s="58"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
+      <c r="G62" s="38"/>
       <c r="H62" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="57"/>
+      <c r="A63" s="58"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
+      <c r="G63" s="38"/>
       <c r="H63" s="18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="57"/>
+      <c r="A64" s="58"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="40" t="s">
-        <v>70</v>
+      <c r="G64" s="38"/>
+      <c r="H64" s="41" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="52"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="41" t="s">
-        <v>74</v>
+      <c r="G65" s="40"/>
+      <c r="H65" s="42" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B66" s="64"/>
-      <c r="C66" s="65"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="65"/>
-      <c r="H66" s="66"/>
+        <v>79</v>
+      </c>
+      <c r="B66" s="65"/>
+      <c r="C66" s="66"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="67"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="51" t="s">
-        <v>76</v>
+      <c r="A67" s="52" t="s">
+        <v>80</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>15</v>
@@ -8229,29 +8233,29 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="57"/>
+      <c r="A68" s="58"/>
       <c r="B68" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="32" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G68" s="30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="57"/>
+      <c r="A69" s="58"/>
       <c r="B69" s="36" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -8262,282 +8266,258 @@
       </c>
       <c r="H69" s="31"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="58"/>
-      <c r="B70" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="58"/>
-      <c r="B71" s="2" t="s">
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="53"/>
+      <c r="B70" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="H70" s="29"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="62"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="64"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="15"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="58"/>
+      <c r="B73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="18"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="58"/>
+      <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="31"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="52"/>
-      <c r="B72" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="29"/>
-    </row>
-    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B73" s="61"/>
-      <c r="C73" s="62"/>
-      <c r="D73" s="62"/>
-      <c r="E73" s="62"/>
-      <c r="F73" s="62"/>
-      <c r="G73" s="62"/>
-      <c r="H73" s="63"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="15"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="57"/>
-      <c r="B75" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="18"/>
+      <c r="C74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="18"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="53"/>
+      <c r="B75" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="17"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="57"/>
-      <c r="B76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A76" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="18"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="52"/>
-      <c r="B77" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="17"/>
+      <c r="G76" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" s="39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="58"/>
+      <c r="B77" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="H77" s="39" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B78" s="37" t="s">
-        <v>50</v>
-      </c>
+      <c r="A78" s="58"/>
+      <c r="B78" s="37"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="G78" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="57"/>
-      <c r="B79" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="H79" s="39" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="57"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="2" t="s">
+      <c r="F78" s="1"/>
+      <c r="G78" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="19" t="s">
+      <c r="H78" s="19" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="53"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="62"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="64"/>
+    </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="52"/>
-      <c r="B81" s="35"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>85</v>
-      </c>
+      <c r="A81" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="62"/>
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="64"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B82" s="61"/>
-      <c r="C82" s="62"/>
-      <c r="D82" s="62"/>
-      <c r="E82" s="62"/>
-      <c r="F82" s="62"/>
-      <c r="G82" s="62"/>
-      <c r="H82" s="63"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="61"/>
-      <c r="C83" s="62"/>
-      <c r="D83" s="62"/>
-      <c r="E83" s="62"/>
-      <c r="F83" s="62"/>
-      <c r="G83" s="62"/>
-      <c r="H83" s="63"/>
+        <v>92</v>
+      </c>
+      <c r="B82" s="62"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="64"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" s="14"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="61"/>
-      <c r="C84" s="62"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62"/>
-      <c r="G84" s="62"/>
-      <c r="H84" s="63"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="52"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-      <c r="H86" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" s="61"/>
-      <c r="C87" s="62"/>
-      <c r="D87" s="62"/>
-      <c r="E87" s="62"/>
-      <c r="F87" s="62"/>
-      <c r="G87" s="62"/>
-      <c r="H87" s="63"/>
-    </row>
-    <row r="88" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="60"/>
-      <c r="C88" s="60"/>
-      <c r="D88" s="60"/>
-      <c r="E88" s="60"/>
-      <c r="F88" s="60"/>
-      <c r="G88" s="60"/>
-      <c r="H88" s="60"/>
+      <c r="A84" s="53"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" s="62"/>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="64"/>
+    </row>
+    <row r="86" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="61"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B71:H71"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B81:H81"/>
     <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
-    <mergeCell ref="B84:H84"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A83:A84"/>
     <mergeCell ref="A58:A65"/>
-    <mergeCell ref="A67:A72"/>
-    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A72:A75"/>
     <mergeCell ref="A40:A53"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A56:A57"/>
@@ -8573,36 +8553,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="B4" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="68" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
+      <c r="B5" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8709,7 +8689,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -8726,7 +8706,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -8743,7 +8723,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -8760,7 +8740,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8777,7 +8757,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8794,7 +8774,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8811,7 +8791,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8828,7 +8808,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8845,7 +8825,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8862,7 +8842,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8879,7 +8859,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8896,7 +8876,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8913,7 +8893,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8930,7 +8910,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8947,7 +8927,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8964,7 +8944,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8981,7 +8961,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8998,7 +8978,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -9015,7 +8995,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -9032,7 +9012,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -9049,7 +9029,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -9066,7 +9046,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -9116,40 +9096,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0596284D-392B-425B-9D8C-C4B76A4CD3CB}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D784EBAE-10AA-4FE8-8D3B-D4834199FB76}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="121">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -548,7 +548,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -814,11 +814,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1022,6 +1055,18 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5143,13 +5188,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5231,13 +5276,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5263,94 +5308,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5374,10 +5331,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5395,50 +5352,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5462,10 +5375,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5493,23 +5406,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5550,6 +5507,94 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -6551,13 +6596,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6802,6 +6847,94 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2979964" y="14573250"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B305B9D-DC30-46AA-9914-884A58D72DCB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20859750" y="11470821"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0632FD73-32F7-40FA-A4AD-623CAF655FA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20859750" y="15348857"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7183,7 +7316,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="44.7109375" customWidth="1"/>
@@ -8388,76 +8521,74 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="57"/>
+      <c r="A79" s="56"/>
       <c r="B79" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="H79" s="39" t="s">
-        <v>83</v>
-      </c>
+      <c r="G79" s="38"/>
+      <c r="H79" s="39"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="57"/>
+      <c r="A80" s="56"/>
       <c r="B80" s="37"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="71" t="s">
+        <v>70</v>
+      </c>
+      <c r="H80" s="69" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="57"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="H81" s="70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="57"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="19" t="s">
+      <c r="H82" s="19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="52"/>
-      <c r="B81" s="35"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16" t="s">
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="52"/>
+      <c r="B83" s="35"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H81" s="17" t="s">
+      <c r="H83" s="17" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B82" s="61"/>
-      <c r="C82" s="62"/>
-      <c r="D82" s="62"/>
-      <c r="E82" s="62"/>
-      <c r="F82" s="62"/>
-      <c r="G82" s="62"/>
-      <c r="H82" s="63"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" s="61"/>
-      <c r="C83" s="62"/>
-      <c r="D83" s="62"/>
-      <c r="E83" s="62"/>
-      <c r="F83" s="62"/>
-      <c r="G83" s="62"/>
-      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B84" s="61"/>
       <c r="C84" s="62"/>
@@ -8467,60 +8598,84 @@
       <c r="G84" s="62"/>
       <c r="H84" s="63"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="51" t="s">
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" s="61"/>
+      <c r="C85" s="62"/>
+      <c r="D85" s="62"/>
+      <c r="E85" s="62"/>
+      <c r="F85" s="62"/>
+      <c r="G85" s="62"/>
+      <c r="H85" s="63"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B86" s="61"/>
+      <c r="C86" s="62"/>
+      <c r="D86" s="62"/>
+      <c r="E86" s="62"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="62"/>
+      <c r="H86" s="63"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13" t="s">
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E85" s="13" t="s">
+      <c r="E87" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="15" t="s">
+      <c r="F87" s="14"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="52"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16" t="s">
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="52"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E86" s="16" t="s">
+      <c r="E88" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-      <c r="H86" s="17" t="s">
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="12" t="s">
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B87" s="61"/>
-      <c r="C87" s="62"/>
-      <c r="D87" s="62"/>
-      <c r="E87" s="62"/>
-      <c r="F87" s="62"/>
-      <c r="G87" s="62"/>
-      <c r="H87" s="63"/>
-    </row>
-    <row r="88" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="60"/>
-      <c r="C88" s="60"/>
-      <c r="D88" s="60"/>
-      <c r="E88" s="60"/>
-      <c r="F88" s="60"/>
-      <c r="G88" s="60"/>
-      <c r="H88" s="60"/>
+      <c r="B89" s="61"/>
+      <c r="C89" s="62"/>
+      <c r="D89" s="62"/>
+      <c r="E89" s="62"/>
+      <c r="F89" s="62"/>
+      <c r="G89" s="62"/>
+      <c r="H89" s="63"/>
+    </row>
+    <row r="90" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="60"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="60"/>
+      <c r="E90" s="60"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
+      <c r="H90" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -8528,13 +8683,13 @@
     <mergeCell ref="B73:H73"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="B82:H82"/>
-    <mergeCell ref="B83:H83"/>
+    <mergeCell ref="B90:H90"/>
     <mergeCell ref="B84:H84"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="A87:A88"/>
     <mergeCell ref="A58:A65"/>
     <mergeCell ref="A67:A72"/>
     <mergeCell ref="A74:A77"/>

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D784EBAE-10AA-4FE8-8D3B-D4834199FB76}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8506629-198B-46B4-BB05-22D33D784385}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="122">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>16:00/24:00</t>
+  </si>
+  <si>
+    <t>11:00/13:00</t>
   </si>
 </sst>
 </file>
@@ -548,7 +551,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -815,26 +818,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -851,7 +834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -962,9 +945,6 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1055,18 +1035,16 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5274,50 +5252,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>83</xdr:row>
@@ -6858,6 +6792,94 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0632FD73-32F7-40FA-A4AD-623CAF655FA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20859750" y="15348857"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{429E8ED4-8609-488A-A2C3-C7846D6F6CE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5959929" y="6041571"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>79</xdr:row>
@@ -6871,70 +6893,26 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B305B9D-DC30-46AA-9914-884A58D72DCB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20859750" y="11470821"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0632FD73-32F7-40FA-A4AD-623CAF655FA8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20859750" y="15348857"/>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3627993A-959C-472C-96B2-FBAB2B8D9FD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11919857" y="1755321"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7323,28 +7301,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50" t="s">
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
@@ -7399,18 +7377,18 @@
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="50" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13"/>
@@ -7426,7 +7404,7 @@
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="52"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -7440,7 +7418,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="55" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -7451,7 +7429,7 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="45" t="s">
         <v>108</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -7460,7 +7438,7 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
+      <c r="A9" s="56"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -7469,7 +7447,7 @@
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="46" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -7478,7 +7456,7 @@
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="57"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
@@ -7487,14 +7465,14 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="44" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="57"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -7510,21 +7488,21 @@
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="57"/>
+      <c r="A12" s="56"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="44" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="52"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16" t="s">
@@ -7538,7 +7516,7 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="50" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="13"/>
@@ -7552,7 +7530,7 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="52"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16" t="s">
         <v>16</v>
@@ -7564,7 +7542,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="50" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="13"/>
@@ -7578,7 +7556,7 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="52"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16" t="s">
@@ -7590,7 +7568,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="50" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -7610,7 +7588,7 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="52"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="16" t="s">
         <v>30</v>
       </c>
@@ -7628,7 +7606,7 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="50" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="13"/>
@@ -7646,7 +7624,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
@@ -7662,39 +7640,39 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="50" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="49" t="s">
+      <c r="F22" s="48" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="57"/>
+      <c r="A23" s="56"/>
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="41" t="s">
         <v>37</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="41" t="s">
         <v>37</v>
       </c>
       <c r="F23" s="23" t="s">
@@ -7704,17 +7682,17 @@
       <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="57"/>
+      <c r="A24" s="56"/>
       <c r="B24" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="42" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="23"/>
@@ -7722,17 +7700,17 @@
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="57"/>
+      <c r="A25" s="56"/>
       <c r="B25" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="42" t="s">
+      <c r="E25" s="41" t="s">
         <v>40</v>
       </c>
       <c r="F25" s="23"/>
@@ -7740,31 +7718,31 @@
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="57"/>
+      <c r="A26" s="56"/>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
       <c r="F26" s="23"/>
       <c r="G26" s="1"/>
       <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="52"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
       <c r="F27" s="24"/>
       <c r="G27" s="16"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="50" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="13"/>
@@ -7782,7 +7760,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="59"/>
+      <c r="A29" s="58"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -7798,7 +7776,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
+      <c r="A30" s="58"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -7810,7 +7788,7 @@
       <c r="H30" s="31"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="58"/>
+      <c r="A31" s="57"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -7822,7 +7800,7 @@
       <c r="H31" s="31"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="50" t="s">
         <v>46</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -7844,7 +7822,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="57"/>
+      <c r="A33" s="56"/>
       <c r="B33" s="1" t="s">
         <v>47</v>
       </c>
@@ -7864,7 +7842,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="57"/>
+      <c r="A34" s="56"/>
       <c r="B34" s="1"/>
       <c r="C34" s="36" t="s">
         <v>50</v>
@@ -7878,7 +7856,7 @@
       <c r="H34" s="31"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="52"/>
+      <c r="A35" s="51"/>
       <c r="B35" s="16"/>
       <c r="C35" s="35" t="s">
         <v>51</v>
@@ -7892,7 +7870,7 @@
       <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="51" t="s">
+      <c r="A36" s="50" t="s">
         <v>52</v>
       </c>
       <c r="B36" s="13"/>
@@ -7906,7 +7884,7 @@
       <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="52"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -7921,28 +7899,28 @@
       <c r="A38" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="63"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="62"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="61"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="63"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="62"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="55" t="s">
         <v>56</v>
       </c>
       <c r="B40" s="30" t="s">
@@ -7961,7 +7939,7 @@
       <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="57"/>
+      <c r="A41" s="56"/>
       <c r="B41" s="30" t="s">
         <v>57</v>
       </c>
@@ -7979,7 +7957,7 @@
       <c r="H41" s="18"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="57"/>
+      <c r="A42" s="56"/>
       <c r="B42" s="33" t="s">
         <v>58</v>
       </c>
@@ -7997,7 +7975,7 @@
       <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="57"/>
+      <c r="A43" s="56"/>
       <c r="B43" s="30" t="s">
         <v>59</v>
       </c>
@@ -8015,7 +7993,7 @@
       <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="57"/>
+      <c r="A44" s="56"/>
       <c r="B44" s="33" t="s">
         <v>20</v>
       </c>
@@ -8033,7 +8011,7 @@
       <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="57"/>
+      <c r="A45" s="56"/>
       <c r="B45" s="30" t="s">
         <v>60</v>
       </c>
@@ -8051,7 +8029,7 @@
       <c r="H45" s="18"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="57"/>
+      <c r="A46" s="56"/>
       <c r="B46" s="33" t="s">
         <v>58</v>
       </c>
@@ -8069,7 +8047,7 @@
       <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="57"/>
+      <c r="A47" s="56"/>
       <c r="B47" s="30" t="s">
         <v>61</v>
       </c>
@@ -8087,7 +8065,7 @@
       <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="57"/>
+      <c r="A48" s="56"/>
       <c r="B48" s="33" t="s">
         <v>20</v>
       </c>
@@ -8105,7 +8083,7 @@
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="57"/>
+      <c r="A49" s="56"/>
       <c r="B49" s="30" t="s">
         <v>62</v>
       </c>
@@ -8123,7 +8101,7 @@
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="57"/>
+      <c r="A50" s="56"/>
       <c r="B50" s="33" t="s">
         <v>58</v>
       </c>
@@ -8139,7 +8117,7 @@
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="57"/>
+      <c r="A51" s="56"/>
       <c r="B51" s="30" t="s">
         <v>63</v>
       </c>
@@ -8155,7 +8133,7 @@
       <c r="H51" s="18"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="57"/>
+      <c r="A52" s="56"/>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="33" t="s">
@@ -8167,7 +8145,7 @@
       <c r="H52" s="18"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="52"/>
+      <c r="A53" s="51"/>
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28" t="s">
@@ -8179,7 +8157,7 @@
       <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="51" t="s">
+      <c r="A54" s="50" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="13"/>
@@ -8191,7 +8169,7 @@
       <c r="H54" s="15"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="52"/>
+      <c r="A55" s="51"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -8201,7 +8179,7 @@
       <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="51" t="s">
+      <c r="A56" s="50" t="s">
         <v>66</v>
       </c>
       <c r="B56" s="13"/>
@@ -8217,7 +8195,7 @@
       <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="52"/>
+      <c r="A57" s="51"/>
       <c r="B57" s="16"/>
       <c r="C57" s="35" t="s">
         <v>67</v>
@@ -8231,7 +8209,7 @@
       <c r="H57" s="17"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="55" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="1"/>
@@ -8244,7 +8222,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="57"/>
+      <c r="A59" s="56"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -8256,31 +8234,31 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="57"/>
+      <c r="A60" s="56"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="40" t="s">
+      <c r="H60" s="39" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="57"/>
+      <c r="A61" s="56"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="39" t="s">
+      <c r="H61" s="38" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="57"/>
+      <c r="A62" s="56"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -8292,7 +8270,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="57"/>
+      <c r="A63" s="56"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -8304,26 +8282,26 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="57"/>
+      <c r="A64" s="56"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="40" t="s">
+      <c r="H64" s="39" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="52"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
       <c r="G65" s="16"/>
-      <c r="H65" s="41" t="s">
+      <c r="H65" s="40" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8331,16 +8309,16 @@
       <c r="A66" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="64"/>
-      <c r="C66" s="65"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="65"/>
-      <c r="H66" s="66"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="65"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="51" t="s">
+      <c r="A67" s="50" t="s">
         <v>76</v>
       </c>
       <c r="B67" s="13" t="s">
@@ -8362,7 +8340,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="57"/>
+      <c r="A68" s="56"/>
       <c r="B68" s="1" t="s">
         <v>77</v>
       </c>
@@ -8382,7 +8360,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="57"/>
+      <c r="A69" s="56"/>
       <c r="B69" s="36" t="s">
         <v>50</v>
       </c>
@@ -8396,7 +8374,7 @@
       <c r="H69" s="31"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="58"/>
+      <c r="A70" s="57"/>
       <c r="B70" s="37" t="s">
         <v>68</v>
       </c>
@@ -8410,7 +8388,7 @@
       <c r="H70" s="31"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="58"/>
+      <c r="A71" s="57"/>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
@@ -8422,7 +8400,7 @@
       <c r="H71" s="31"/>
     </row>
     <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="52"/>
+      <c r="A72" s="51"/>
       <c r="B72" s="16" t="s">
         <v>116</v>
       </c>
@@ -8437,16 +8415,16 @@
       <c r="A73" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="61"/>
-      <c r="C73" s="62"/>
-      <c r="D73" s="62"/>
-      <c r="E73" s="62"/>
-      <c r="F73" s="62"/>
-      <c r="G73" s="62"/>
-      <c r="H73" s="63"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="61"/>
+      <c r="E73" s="61"/>
+      <c r="F73" s="61"/>
+      <c r="G73" s="61"/>
+      <c r="H73" s="62"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="51" t="s">
+      <c r="A74" s="50" t="s">
         <v>79</v>
       </c>
       <c r="B74" s="13" t="s">
@@ -8462,7 +8440,7 @@
       <c r="H74" s="15"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="57"/>
+      <c r="A75" s="56"/>
       <c r="B75" s="1" t="s">
         <v>80</v>
       </c>
@@ -8476,7 +8454,7 @@
       <c r="H75" s="18"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="57"/>
+      <c r="A76" s="56"/>
       <c r="B76" s="2" t="s">
         <v>15</v>
       </c>
@@ -8490,7 +8468,7 @@
       <c r="H76" s="18"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="52"/>
+      <c r="A77" s="51"/>
       <c r="B77" s="16" t="s">
         <v>81</v>
       </c>
@@ -8504,62 +8482,69 @@
       <c r="H77" s="17"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="56" t="s">
+      <c r="A78" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="37" t="s">
+      <c r="B78" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="G78" s="38" t="s">
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="H78" s="39" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="56"/>
+      <c r="A79" s="55"/>
       <c r="B79" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="39"/>
+      <c r="F79" s="71"/>
+      <c r="G79" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H79" s="38" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="56"/>
+      <c r="A80" s="55"/>
       <c r="B80" s="37"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
-      <c r="G80" s="71" t="s">
+      <c r="F80" s="71"/>
+      <c r="G80" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="H80" s="69" t="s">
-        <v>70</v>
+      <c r="H80" s="19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="57"/>
+      <c r="A81" s="56"/>
       <c r="B81" s="37"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="72" t="s">
+      <c r="G81" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="H81" s="70" t="s">
-        <v>83</v>
+      <c r="H81" s="18" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="57"/>
+      <c r="A82" s="56"/>
       <c r="B82" s="37"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -8568,12 +8553,10 @@
       <c r="G82" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H82" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="H82" s="18"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="52"/>
+      <c r="A83" s="51"/>
       <c r="B83" s="35"/>
       <c r="C83" s="16"/>
       <c r="D83" s="16"/>
@@ -8582,48 +8565,46 @@
       <c r="G83" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H83" s="17" t="s">
-        <v>85</v>
-      </c>
+      <c r="H83" s="17"/>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B84" s="61"/>
-      <c r="C84" s="62"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62"/>
-      <c r="G84" s="62"/>
-      <c r="H84" s="63"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="61"/>
+      <c r="D84" s="61"/>
+      <c r="E84" s="61"/>
+      <c r="F84" s="61"/>
+      <c r="G84" s="61"/>
+      <c r="H84" s="62"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B85" s="61"/>
-      <c r="C85" s="62"/>
-      <c r="D85" s="62"/>
-      <c r="E85" s="62"/>
-      <c r="F85" s="62"/>
-      <c r="G85" s="62"/>
-      <c r="H85" s="63"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="61"/>
+      <c r="D85" s="61"/>
+      <c r="E85" s="61"/>
+      <c r="F85" s="61"/>
+      <c r="G85" s="61"/>
+      <c r="H85" s="62"/>
     </row>
     <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B86" s="61"/>
-      <c r="C86" s="62"/>
-      <c r="D86" s="62"/>
-      <c r="E86" s="62"/>
-      <c r="F86" s="62"/>
-      <c r="G86" s="62"/>
-      <c r="H86" s="63"/>
+      <c r="B86" s="60"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="62"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="51" t="s">
+      <c r="A87" s="50" t="s">
         <v>89</v>
       </c>
       <c r="B87" s="13"/>
@@ -8641,7 +8622,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="52"/>
+      <c r="A88" s="51"/>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
       <c r="D88" s="16" t="s">
@@ -8660,22 +8641,22 @@
       <c r="A89" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B89" s="61"/>
-      <c r="C89" s="62"/>
-      <c r="D89" s="62"/>
-      <c r="E89" s="62"/>
-      <c r="F89" s="62"/>
-      <c r="G89" s="62"/>
-      <c r="H89" s="63"/>
+      <c r="B89" s="60"/>
+      <c r="C89" s="61"/>
+      <c r="D89" s="61"/>
+      <c r="E89" s="61"/>
+      <c r="F89" s="61"/>
+      <c r="G89" s="61"/>
+      <c r="H89" s="62"/>
     </row>
     <row r="90" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="60"/>
-      <c r="C90" s="60"/>
-      <c r="D90" s="60"/>
-      <c r="E90" s="60"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="60"/>
-      <c r="H90" s="60"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="59"/>
+      <c r="D90" s="59"/>
+      <c r="E90" s="59"/>
+      <c r="F90" s="59"/>
+      <c r="G90" s="59"/>
+      <c r="H90" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -8728,20 +8709,20 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">

--- a/Plannings 2026 S18.xlsx
+++ b/Plannings 2026 S18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8506629-198B-46B4-BB05-22D33D784385}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{CA6A0DFE-E57C-4974-A26C-1035092EF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF97EFE7-7996-45EC-B71C-D43E8CBB8AEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="120">
   <si>
     <t>Planning des salariés du 27/04/2026 au 03/05/2026</t>
   </si>
@@ -121,9 +121,18 @@
     <t>11:45/22:00</t>
   </si>
   <si>
+    <t>11:30/17:00</t>
+  </si>
+  <si>
+    <t>11:35/17:00</t>
+  </si>
+  <si>
     <t>CRUZEL Quentin</t>
   </si>
   <si>
+    <t>16:30/24:00</t>
+  </si>
+  <si>
     <t>DE NOUEL Maxime</t>
   </si>
   <si>
@@ -238,6 +247,9 @@
     <t>ANNIV</t>
   </si>
   <si>
+    <t>14:00/18:00</t>
+  </si>
+  <si>
     <t>09:30/10:15</t>
   </si>
   <si>
@@ -371,24 +383,6 @@
   </si>
   <si>
     <t>CUP France 26 // ANNIV</t>
-  </si>
-  <si>
-    <t>21:30/24:00</t>
-  </si>
-  <si>
-    <t>11:45/17:00</t>
-  </si>
-  <si>
-    <t>11:45/17:25</t>
-  </si>
-  <si>
-    <t>17:45/24:00</t>
-  </si>
-  <si>
-    <t>16:00/24:00</t>
-  </si>
-  <si>
-    <t>11:00/13:00</t>
   </si>
 </sst>
 </file>
@@ -551,7 +545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -817,24 +811,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -945,7 +926,13 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1035,16 +1022,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4284,6 +4261,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>57</xdr:row>
@@ -4770,13 +4791,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4814,6 +4835,50 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -4825,10 +4890,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4856,23 +4965,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4900,103 +5009,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5034,13 +5055,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5078,109 +5099,197 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5208,59 +5317,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5286,6 +5351,226 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5309,226 +5594,6 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
- 